--- a/07_supplementary/Supplementary_File_3.xlsx
+++ b/07_supplementary/Supplementary_File_3.xlsx
@@ -67,11 +67,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -614,7 +618,6 @@
           <t>Evaluation of the use of PEEK material in post-core and crown restorations using finite element analysis</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Am J Dent</t>
@@ -16010,7 +16013,6 @@
           <t>First steps of a digital workflow to build up a virtual articulator using open-source Autodesk Meshmixer software</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>Int J Comput Dent</t>
@@ -16146,7 +16148,6 @@
           <t>3D printing in endodontics: report of three clinical cases with innovative approaches</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>Int J Comput Dent</t>
@@ -39717,8 +39718,6 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="inlineStr"/>
-      <c r="B562" t="inlineStr"/>
       <c r="C562" t="inlineStr">
         <is>
           <t>Influence of splinting scan bodies or incorporating three-dimensionally printed scan aids on the trueness of complete arch digital scans.</t>
@@ -39762,7 +39761,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
           <t>SolidWorks;Geomagic Control X</t>
@@ -39775,8 +39773,6 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="inlineStr"/>
-      <c r="B563" t="inlineStr"/>
       <c r="C563" t="inlineStr">
         <is>
           <t>Time-resolved prediction of dental implant biomechanics through integration of finite element analysis, osseointegration dynamics, and deep learning</t>
@@ -39820,7 +39816,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
           <t>SolidWorks;ANSYS Workbench</t>
@@ -39833,8 +39828,6 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="inlineStr"/>
-      <c r="B564" t="inlineStr"/>
       <c r="C564" t="inlineStr">
         <is>
           <t>Randomized crossover study of immersive planning in craniomaxillofacial trauma comparing virtual reality and workstation workflows</t>
@@ -39878,7 +39871,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -39891,8 +39883,6 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="inlineStr"/>
-      <c r="B565" t="inlineStr"/>
       <c r="C565" t="inlineStr">
         <is>
           <t>Accuracy of DICOM-DICOM vs. DICOM-STL Protocols in Computer-Guided Surgery: A Human Clinical Study</t>
@@ -39936,7 +39926,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
         <is>
           <t>Geomagic (unspecified)</t>
@@ -39949,8 +39938,6 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="inlineStr"/>
-      <c r="B566" t="inlineStr"/>
       <c r="C566" t="inlineStr">
         <is>
           <t>A novel approach to craniofacial analysis using automated 3D landmarking of the skull</t>
@@ -39994,7 +39981,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;Meshmixer</t>
@@ -40007,8 +39993,6 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="inlineStr"/>
-      <c r="B567" t="inlineStr"/>
       <c r="C567" t="inlineStr">
         <is>
           <t>Development of 3D in vitro mineralized bone model to reproduce dental implants osseointegration process.</t>
@@ -40052,7 +40036,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
         <is>
           <t>Fusion 360;ImageJ</t>
@@ -40065,8 +40048,6 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="inlineStr"/>
-      <c r="B568" t="inlineStr"/>
       <c r="C568" t="inlineStr">
         <is>
           <t>An in vitro evaluation of bond strength and failure behavior between 3D-printed cobalt-chromium alloy and different types of denture base resins</t>
@@ -40110,7 +40091,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr">
         <is>
           <t>Meshmixer;Magics</t>
@@ -40123,8 +40103,6 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="inlineStr"/>
-      <c r="B569" t="inlineStr"/>
       <c r="C569" t="inlineStr">
         <is>
           <t>The geometric relationship between root length and root surface area determined from digital tooth models.</t>
@@ -40168,7 +40146,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L569" t="inlineStr"/>
       <c r="M569" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -40181,8 +40158,6 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="inlineStr"/>
-      <c r="B570" t="inlineStr"/>
       <c r="C570" t="inlineStr">
         <is>
           <t>Accuracy of facial skeletal surfaces segmented from CT and CBCT radiographs</t>
@@ -40226,7 +40201,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr"/>
       <c r="M570" t="inlineStr">
         <is>
           <t>Artec Studio</t>
@@ -40239,8 +40213,6 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="inlineStr"/>
-      <c r="B571" t="inlineStr"/>
       <c r="C571" t="inlineStr">
         <is>
           <t>Multi-Material 3D Printing of a Customized Sports Mouth Guard: Proof-of-Concept Clinical Case</t>
@@ -40284,7 +40256,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr"/>
       <c r="M571" t="inlineStr">
         <is>
           <t>ZBrush</t>
@@ -40297,8 +40268,6 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="inlineStr"/>
-      <c r="B572" t="inlineStr"/>
       <c r="C572" t="inlineStr">
         <is>
           <t>Is All-on-four effective in case of partial mandibular resection? A 3D finite element study</t>
@@ -40342,7 +40311,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr"/>
       <c r="M572" t="inlineStr">
         <is>
           <t>Mimics;SolidWorks;ANSYS</t>
@@ -40355,8 +40323,6 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr"/>
-      <c r="B573" t="inlineStr"/>
       <c r="C573" t="inlineStr">
         <is>
           <t>Development of an experimental model for assessment of palatal tissue decomposition by intraoral scanner.</t>
@@ -40400,7 +40366,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -40413,8 +40378,6 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr"/>
-      <c r="B574" t="inlineStr"/>
       <c r="C574" t="inlineStr">
         <is>
           <t>Feasibility study and material selection for powder-bed fusion process in printing of denture clasps.</t>
@@ -40458,7 +40421,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr"/>
       <c r="M574" t="inlineStr">
         <is>
           <t>Geomagic Studio;Magics</t>
@@ -40471,8 +40433,6 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr"/>
-      <c r="B575" t="inlineStr"/>
       <c r="C575" t="inlineStr">
         <is>
           <t>Ortho-OPD: An Automatic Osteotomy Planes Design Model for Orthognathic Surgery Based on Deep Learning</t>
@@ -40516,7 +40476,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr"/>
       <c r="M575" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -40529,8 +40488,6 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr"/>
-      <c r="B576" t="inlineStr"/>
       <c r="C576" t="inlineStr">
         <is>
           <t>Realization of a Dental Framework by 3D Printing in Material Cobalt-Chromium with Superior Precision and Fitting Accuracy</t>
@@ -40574,7 +40531,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr"/>
       <c r="M576" t="inlineStr">
         <is>
           <t>GOM ATOS Professional</t>
@@ -40587,8 +40543,6 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr"/>
-      <c r="B577" t="inlineStr"/>
       <c r="C577" t="inlineStr">
         <is>
           <t>Assessing the Effect of Interimplant Distance and Angle on Different Impression Techniques</t>
@@ -40632,7 +40586,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr"/>
       <c r="M577" t="inlineStr">
         <is>
           <t>RapidForm</t>
@@ -40645,8 +40598,6 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr"/>
-      <c r="B578" t="inlineStr"/>
       <c r="C578" t="inlineStr">
         <is>
           <t>The impact of mixed reality training method on novice trainees of dental implants: an in vitro study</t>
@@ -40690,7 +40641,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr"/>
       <c r="M578" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -40703,8 +40653,6 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr"/>
-      <c r="B579" t="inlineStr"/>
       <c r="C579" t="inlineStr">
         <is>
           <t>Sex and age biological variation of the mandible in a Portuguese population- a forensic and medico-legal approaches with three-dimensional analysis</t>
@@ -40748,7 +40696,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr"/>
       <c r="M579" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -40761,8 +40708,6 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr"/>
-      <c r="B580" t="inlineStr"/>
       <c r="C580" t="inlineStr">
         <is>
           <t>Virtual reality and 3D printing in head and neck cancer: an educational experience</t>
@@ -40806,7 +40751,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr"/>
       <c r="M580" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -40819,8 +40763,6 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr"/>
-      <c r="B581" t="inlineStr"/>
       <c r="C581" t="inlineStr">
         <is>
           <t>Evaluation of Root Angulations Through Panoramic Films Using Artificial Intelligence</t>
@@ -40864,7 +40806,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -40877,8 +40818,6 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr"/>
-      <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr">
         <is>
           <t>Precise sparse-view dental crown reconstruction via 3D Gaussian neural fields</t>
@@ -40922,7 +40861,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L582" t="inlineStr"/>
       <c r="M582" t="inlineStr">
         <is>
           <t>CloudCompare</t>
@@ -40935,8 +40873,6 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr"/>
-      <c r="B583" t="inlineStr"/>
       <c r="C583" t="inlineStr">
         <is>
           <t>Influence of age-related changes on crack growth trajectories and toughening mechanisms in human dentin</t>
@@ -40980,7 +40916,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L583" t="inlineStr"/>
       <c r="M583" t="inlineStr">
         <is>
           <t>ABAQUS</t>
@@ -40993,8 +40928,6 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr"/>
-      <c r="B584" t="inlineStr"/>
       <c r="C584" t="inlineStr">
         <is>
           <t>Combining 3D Multi-Object Reconstruction with Finite Element Analysis for Accurate Dental Modelling and Restoration</t>
@@ -41038,7 +40971,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L584" t="inlineStr"/>
       <c r="M584" t="inlineStr">
         <is>
           <t>ANSYS</t>
@@ -41051,8 +40983,6 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr"/>
-      <c r="B585" t="inlineStr"/>
       <c r="C585" t="inlineStr">
         <is>
           <t>Lateral stress distribution analysis on hafnium metal bar for implant superstructure- A finite element analysis.</t>
@@ -41096,7 +41026,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L585" t="inlineStr"/>
       <c r="M585" t="inlineStr">
         <is>
           <t>SolidWorks;HyperMesh;ABAQUS</t>
@@ -41109,8 +41038,6 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr"/>
-      <c r="B586" t="inlineStr"/>
       <c r="C586" t="inlineStr">
         <is>
           <t>Evaluation of trueness and precision of removable partial denture metal frameworks manufactured with digital technology and different materials</t>
@@ -41154,7 +41081,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L586" t="inlineStr"/>
       <c r="M586" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -41167,8 +41093,6 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr"/>
-      <c r="B587" t="inlineStr"/>
       <c r="C587" t="inlineStr">
         <is>
           <t>Effect of implant number, attachment type, and framework material on stress distribution in mandibular overdentures: a finite element analysis</t>
@@ -41212,7 +41136,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L587" t="inlineStr"/>
       <c r="M587" t="inlineStr">
         <is>
           <t>3D Slicer;SpaceClaim;ANSYS Workbench;LS-DYNA</t>
@@ -41225,8 +41148,6 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr"/>
-      <c r="B588" t="inlineStr"/>
       <c r="C588" t="inlineStr">
         <is>
           <t>Accuracy evaluation of dental CBCT and scanned model registration method based on pulp horn mapping surface: an in vitro proof-of-concept</t>
@@ -41270,7 +41191,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L588" t="inlineStr"/>
       <c r="M588" t="inlineStr">
         <is>
           <t>Geomagic Wrap</t>
@@ -41283,8 +41203,6 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr"/>
-      <c r="B589" t="inlineStr"/>
       <c r="C589" t="inlineStr">
         <is>
           <t>Enlarge the Error Prediction Dataset in 3-D Printing: An Unsupervised Dental Crown Mesh Generator</t>
@@ -41328,7 +41246,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L589" t="inlineStr"/>
       <c r="M589" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -41341,8 +41258,6 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr"/>
-      <c r="B590" t="inlineStr"/>
       <c r="C590" t="inlineStr">
         <is>
           <t>An application framework of 3D assessment image registration accuracy and untouched surface area in canal instrumentation laboratory research with micro-computed tomography</t>
@@ -41386,7 +41301,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L590" t="inlineStr"/>
       <c r="M590" t="inlineStr">
         <is>
           <t>3D Slicer;MeViSLab</t>
@@ -41399,8 +41313,6 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr"/>
-      <c r="B591" t="inlineStr"/>
       <c r="C591" t="inlineStr">
         <is>
           <t>Comparison between relining of ill-fitted maxillary complete denture versus CAD/CAM milling of new one regarding patient satisfaction, denture retention and adaptation</t>
@@ -41444,7 +41356,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr"/>
       <c r="M591" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -41457,8 +41368,6 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr"/>
-      <c r="B592" t="inlineStr"/>
       <c r="C592" t="inlineStr">
         <is>
           <t>Accuracy of Static Computer- Assisted Implant Placement in Posterior Edentulous Areas with Different Levels of Tooth- Support by Novice Clinicians.</t>
@@ -41502,7 +41411,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L592" t="inlineStr"/>
       <c r="M592" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -41515,8 +41423,6 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr"/>
-      <c r="B593" t="inlineStr"/>
       <c r="C593" t="inlineStr">
         <is>
           <t>Geometric accuracy of magnetic resonance imaging-derived virtual 3-dimensional bone surface models of the mandible in comparison to computed tomography and cone beam computed tomography: A porcine cadaver study</t>
@@ -41560,7 +41466,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L593" t="inlineStr"/>
       <c r="M593" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -41573,8 +41478,6 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr"/>
-      <c r="B594" t="inlineStr"/>
       <c r="C594" t="inlineStr">
         <is>
           <t>Three-Dimensional Hemisided Analysis of the Pharyngeal Airway: A Novel Technical Strategy to Evaluate Asymmetric Remodeling After Orthognathic Surgery</t>
@@ -41618,7 +41521,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L594" t="inlineStr"/>
       <c r="M594" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -41631,8 +41533,6 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr"/>
-      <c r="B595" t="inlineStr"/>
       <c r="C595" t="inlineStr">
         <is>
           <t>Digital Workflow with Open-Source CAD-CAM Software Aimed to Design a Customized 3D Laser-Printed Titanium Mesh for Guided Bone Regeneration</t>
@@ -41676,7 +41576,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L595" t="inlineStr"/>
       <c r="M595" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -41689,8 +41588,6 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr"/>
-      <c r="B596" t="inlineStr"/>
       <c r="C596" t="inlineStr">
         <is>
           <t>Evaluation of Zirconia and High Performance Polymer Abutment Surface Roughness and Stress Concentration for Implant-Supported Fixed Dental Prostheses</t>
@@ -41734,7 +41631,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L596" t="inlineStr"/>
       <c r="M596" t="inlineStr">
         <is>
           <t>Rhinoceros;ANSYS</t>
@@ -41747,8 +41643,6 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr"/>
-      <c r="B597" t="inlineStr"/>
       <c r="C597" t="inlineStr">
         <is>
           <t>A micro-CT-integrated 3D simulation framework reveals fluid transport mechanisms and void dynamics in root canal biomaterials</t>
@@ -41792,7 +41686,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -41805,8 +41698,6 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr"/>
-      <c r="B598" t="inlineStr"/>
       <c r="C598" t="inlineStr">
         <is>
           <t>Biomechanical analysis of All-on-4 implant supported framework using different materials across various clinical practice</t>
@@ -41850,7 +41741,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Studio;SolidWorks;ANSYS</t>
@@ -41863,8 +41753,6 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr"/>
-      <c r="B599" t="inlineStr"/>
       <c r="C599" t="inlineStr">
         <is>
           <t>Development and validation of a robotic system for milling individualized jawbone cavities in oral and maxillofacial surgery</t>
@@ -41908,7 +41796,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L599" t="inlineStr"/>
       <c r="M599" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Wrap</t>
@@ -41921,8 +41808,6 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr"/>
-      <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr">
         <is>
           <t>A novel digital and visualized guided bone regeneration procedure and digital precise bone augmentation: A case series</t>
@@ -41966,7 +41851,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L600" t="inlineStr"/>
       <c r="M600" t="inlineStr">
         <is>
           <t>3-Matic;Mimics</t>
@@ -41979,8 +41863,6 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr"/>
-      <c r="B601" t="inlineStr"/>
       <c r="C601" t="inlineStr">
         <is>
           <t>Clinical efficacy of maxillary digital removable partial dentures based on direct intraoral scanning and selective laser melting technology: a double-blind randomized controlled crossover clinical trial</t>
@@ -42024,7 +41906,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr"/>
       <c r="M601" t="inlineStr">
         <is>
           <t>Geomagic Studio</t>
@@ -42037,8 +41918,6 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr"/>
-      <c r="B602" t="inlineStr"/>
       <c r="C602" t="inlineStr">
         <is>
           <t>Trueness and marginal fit of implant-supported complete-arch fixed prosthesis frameworks made of high-performance polymers and titanium: An explorative in-vitro study</t>
@@ -42082,7 +41961,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr"/>
       <c r="M602" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -42095,8 +41973,6 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr"/>
-      <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr">
         <is>
           <t>Does Printing Orientation Matter in PolyJet 3D Printed Teeth for Endodontics? A Micro-CT Analysis</t>
@@ -42140,7 +42016,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L603" t="inlineStr"/>
       <c r="M603" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -42153,8 +42028,6 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr"/>
-      <c r="B604" t="inlineStr"/>
       <c r="C604" t="inlineStr">
         <is>
           <t>Three-dimensional facial volume analysis using algorithm-based personalized aesthetic templates</t>
@@ -42198,7 +42071,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr"/>
       <c r="M604" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -42211,8 +42083,6 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr"/>
-      <c r="B605" t="inlineStr"/>
       <c r="C605" t="inlineStr">
         <is>
           <t>Effect of Palatal Vault Depth on the Trueness of Metal Laser-Sintered and Cast Cobalt-Chromium Removable Partial Denture Frameworks</t>
@@ -42256,7 +42126,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr"/>
       <c r="M605" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -42269,8 +42138,6 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr"/>
-      <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr">
         <is>
           <t>Individual, High-Precision 3D Mandibular Model for Finite Element Analysis of Three-Unit Bridges: A Biomechanical Pilot Study.</t>
@@ -42314,7 +42181,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr"/>
       <c r="M606" t="inlineStr">
         <is>
           <t>3D Slicer;ABAQUS;Creo</t>
@@ -42327,8 +42193,6 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr"/>
-      <c r="B607" t="inlineStr"/>
       <c r="C607" t="inlineStr">
         <is>
           <t>An open-source, three-dimensional growth model of the mandible.</t>
@@ -42372,7 +42236,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr">
         <is>
           <t>Brainlab Elements;Meshmixer</t>
@@ -42385,8 +42248,6 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr"/>
-      <c r="B608" t="inlineStr"/>
       <c r="C608" t="inlineStr">
         <is>
           <t>Effect of printing technology, layer height, and orientation on assessment of 3D-printed models.</t>
@@ -42430,7 +42291,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr"/>
       <c r="M608" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -42443,8 +42303,6 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr"/>
-      <c r="B609" t="inlineStr"/>
       <c r="C609" t="inlineStr">
         <is>
           <t>pH-responsive polydopamine-coated mesoporous silica nanoplatform integrated into 3D-printed PLA/nHA scaffolds for synergistic bone regeneration</t>
@@ -42488,7 +42346,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr"/>
       <c r="M609" t="inlineStr">
         <is>
           <t>Analyze</t>
@@ -42501,8 +42358,6 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr"/>
-      <c r="B610" t="inlineStr"/>
       <c r="C610" t="inlineStr">
         <is>
           <t>TIP, TORQUE &amp; ROTATIONS: How accurately do digital superimposition software packages quantify tooth movement?</t>
@@ -42546,7 +42401,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr"/>
       <c r="M610" t="inlineStr">
         <is>
           <t>Geomagic (unspecified)</t>
@@ -42559,8 +42413,6 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr"/>
-      <c r="B611" t="inlineStr"/>
       <c r="C611" t="inlineStr">
         <is>
           <t>Dimensional measurement accuracy of 3-dimensional models from cone beam computed tomography using different voxel sizes</t>
@@ -42604,7 +42456,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr"/>
       <c r="M611" t="inlineStr">
         <is>
           <t>3D Slicer;Geomagic Qualify</t>
@@ -42617,8 +42468,6 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr"/>
-      <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr">
         <is>
           <t>Digitally-driven optimization of intraoral water jet parameters for plaque removal: a personalized 3D-guided orthogonal study.</t>
@@ -42662,7 +42511,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L612" t="inlineStr"/>
       <c r="M612" t="inlineStr">
         <is>
           <t>Rhinoceros;Geomagic Wrap</t>
@@ -42675,8 +42523,6 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr"/>
-      <c r="B613" t="inlineStr"/>
       <c r="C613" t="inlineStr">
         <is>
           <t>Wear at the implant-framework interface between titanium implant platform and the additively manufactured titanium and cobalt-chromium frameworks</t>
@@ -42720,7 +42566,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L613" t="inlineStr"/>
       <c r="M613" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -42733,8 +42578,6 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr"/>
-      <c r="B614" t="inlineStr"/>
       <c r="C614" t="inlineStr">
         <is>
           <t>Complete 3D Kinematics Parameters of the Temporo-Mandibular Joints Using in Vivo Data Fusion</t>
@@ -42778,7 +42621,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr">
         <is>
           <t>Amira</t>
@@ -42791,8 +42633,6 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr"/>
-      <c r="B615" t="inlineStr"/>
       <c r="C615" t="inlineStr">
         <is>
           <t>A method based on 3D affine alignment for the quantification of palatal expansion</t>
@@ -42836,7 +42676,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L615" t="inlineStr"/>
       <c r="M615" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -42849,8 +42688,6 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr"/>
-      <c r="B616" t="inlineStr"/>
       <c r="C616" t="inlineStr">
         <is>
           <t>The cumulative effect of error in the digital workflow for complete-arch implant-supported frameworks: An in vitro study</t>
@@ -42894,7 +42731,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr"/>
       <c r="M616" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -42907,8 +42743,6 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr"/>
-      <c r="B617" t="inlineStr"/>
       <c r="C617" t="inlineStr">
         <is>
           <t>Automatic multi-class classification of 3D relationships between the mandibular third molar and canal on cone-beam computed tomography using a geometry-aware network</t>
@@ -42952,7 +42786,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr"/>
       <c r="M617" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -42965,8 +42798,6 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr"/>
-      <c r="B618" t="inlineStr"/>
       <c r="C618" t="inlineStr">
         <is>
           <t>Fracture Resistance of Posterior Tooth-Supported Cantilever Fixed Dental Prostheses of Different Zirconia Generations and Framework Thicknesses: An In Vitro Study</t>
@@ -43010,7 +42841,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L618" t="inlineStr"/>
       <c r="M618" t="inlineStr">
         <is>
           <t>Geomagic Design X</t>
@@ -43023,8 +42853,6 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr"/>
-      <c r="B619" t="inlineStr"/>
       <c r="C619" t="inlineStr">
         <is>
           <t>The effects of additive manufacturing technologies and finish line designs on the trueness and dimensional stability of 3D-printed dies</t>
@@ -43068,7 +42896,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr"/>
       <c r="M619" t="inlineStr">
         <is>
           <t>Blender;Geomagic Design X</t>
@@ -43081,8 +42908,6 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr"/>
-      <c r="B620" t="inlineStr"/>
       <c r="C620" t="inlineStr">
         <is>
           <t>A Novel Guided Zygomatic and Pterygoid Implant Surgery System: A Human Cadaver Study on Accuracy.</t>
@@ -43126,7 +42951,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L620" t="inlineStr"/>
       <c r="M620" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -43139,8 +42963,6 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr"/>
-      <c r="B621" t="inlineStr"/>
       <c r="C621" t="inlineStr">
         <is>
           <t>The effect of different tooth preparation finishing procedures and immediate dentin sealing on the scanning accuracy of different intraoral scanners.</t>
@@ -43184,7 +43006,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr"/>
       <c r="M621" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -43197,8 +43018,6 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr"/>
-      <c r="B622" t="inlineStr"/>
       <c r="C622" t="inlineStr">
         <is>
           <t>A Benchmark Dual-Modality Dental Imaging Dataset and a Novel Cognitively Inspired Pipeline for High-Resolution Dental Point Cloud Synthesis</t>
@@ -43242,7 +43061,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr"/>
       <c r="M622" t="inlineStr">
         <is>
           <t>Mimics;MeshLab</t>
@@ -43255,8 +43073,6 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr"/>
-      <c r="B623" t="inlineStr"/>
       <c r="C623" t="inlineStr">
         <is>
           <t>A deep learning framework for automated dental segmentation and diagnostic report generation from cone-beam computed tomography</t>
@@ -43300,7 +43116,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -43313,8 +43128,6 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr"/>
-      <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr">
         <is>
           <t>Augmented Reality-Assisted Micro-Invasive Apicectomy with Markerless Visual-Inertial Odometry: An In Vivo Pilot Study</t>
@@ -43358,7 +43171,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L624" t="inlineStr"/>
       <c r="M624" t="inlineStr">
         <is>
           <t>Mimics;MeshLab</t>
@@ -43371,8 +43183,6 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr"/>
-      <c r="B625" t="inlineStr"/>
       <c r="C625" t="inlineStr">
         <is>
           <t>Continuous Bijection Supervised Pyramid Diffeomorphic Deformation for Learning Tooth Meshes From CBCT Images</t>
@@ -43416,7 +43226,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L625" t="inlineStr"/>
       <c r="M625" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -43429,8 +43238,6 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr"/>
-      <c r="B626" t="inlineStr"/>
       <c r="C626" t="inlineStr">
         <is>
           <t>In vitro comparison of five desktop scanners and an industrial scanner in the evaluation of an intraoral scanner accuracy.</t>
@@ -43474,7 +43281,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L626" t="inlineStr"/>
       <c r="M626" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -43487,8 +43293,6 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr"/>
-      <c r="B627" t="inlineStr"/>
       <c r="C627" t="inlineStr">
         <is>
           <t>Corticotomy Depth as a Modulator of Orthodontic Tooth Movement and PDL Stress-A Finite Element Study</t>
@@ -43532,7 +43336,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L627" t="inlineStr"/>
       <c r="M627" t="inlineStr">
         <is>
           <t>Mimics;HyperMesh</t>
@@ -43545,8 +43348,6 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr"/>
-      <c r="B628" t="inlineStr"/>
       <c r="C628" t="inlineStr">
         <is>
           <t>Microstructural heterogeneity of the collagenous network in the loaded and unloaded periodontal ligament and its biomechanical implications</t>
@@ -43590,7 +43391,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L628" t="inlineStr"/>
       <c r="M628" t="inlineStr">
         <is>
           <t>Simpleware ScanIP</t>
@@ -43603,8 +43403,6 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr"/>
-      <c r="B629" t="inlineStr"/>
       <c r="C629" t="inlineStr">
         <is>
           <t>Influence of the preparation design on the survival probability of occlusal veneers</t>
@@ -43648,7 +43446,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L629" t="inlineStr"/>
       <c r="M629" t="inlineStr">
         <is>
           <t>ITK-SNAP;Z88;ImageJ</t>
@@ -43661,8 +43458,6 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr"/>
-      <c r="B630" t="inlineStr"/>
       <c r="C630" t="inlineStr">
         <is>
           <t>Redefining MRI-Based Skull Segmentation Through AI-Driven Multimodal Integration.</t>
@@ -43706,7 +43501,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L630" t="inlineStr"/>
       <c r="M630" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -43719,8 +43513,6 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr"/>
-      <c r="B631" t="inlineStr"/>
       <c r="C631" t="inlineStr">
         <is>
           <t>Precision-optimized process control in DLP printing of ultra-thin zirconia prostheses: A multi-factor accuracy analysis</t>
@@ -43764,7 +43556,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
         <is>
           <t>Geomagic Wrap</t>
@@ -43777,8 +43568,6 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr"/>
-      <c r="B632" t="inlineStr"/>
       <c r="C632" t="inlineStr">
         <is>
           <t>Metal Organic Framework-Incorporated Three-Dimensional (3D) Bio-Printable Hydrogels to Facilitate Bone Repair: Preparation and In Vitro Bioactivity Analysis</t>
@@ -43822,7 +43611,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr"/>
       <c r="M632" t="inlineStr">
         <is>
           <t>Onshape;Geomagic (unspecified)</t>
@@ -43835,8 +43623,6 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr"/>
-      <c r="B633" t="inlineStr"/>
       <c r="C633" t="inlineStr">
         <is>
           <t>Influence of Framework Material on Stress, Fatigue, and Stability of “All-on-Four” System Components-Biomechanical Evaluation with Finite Element Analysis</t>
@@ -43880,7 +43666,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr"/>
       <c r="M633" t="inlineStr">
         <is>
           <t>Geomagic Design X</t>
@@ -43893,8 +43678,6 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr"/>
-      <c r="B634" t="inlineStr"/>
       <c r="C634" t="inlineStr">
         <is>
           <t>A Machine Learning Pipeline for Cusp Height Prediction in Worn Lower Molars: Methodological Proof-of-Concept and Validation Across Homo</t>
@@ -43938,7 +43721,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L634" t="inlineStr"/>
       <c r="M634" t="inlineStr">
         <is>
           <t>Avizo;MeshLab</t>
@@ -43951,8 +43733,6 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr"/>
-      <c r="B635" t="inlineStr"/>
       <c r="C635" t="inlineStr">
         <is>
           <t>Effect of Different CAD/CAM Milling and 3D Printing Digital Fabrication Techniques on the Accuracy of PMMA Working Models and Vertical Marginal Fit of PMMA Provisional Dental Prosthesis: An In Vitro Study</t>
@@ -43996,7 +43776,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr"/>
       <c r="M635" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -44009,8 +43788,6 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr"/>
-      <c r="B636" t="inlineStr"/>
       <c r="C636" t="inlineStr">
         <is>
           <t>Surgical Navigation, Augmented Reality, and 3D Printing for Hard Palate Adenoid Cystic Carcinoma En-Bloc Resection: Case Report and Literature Review</t>
@@ -44054,7 +43831,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr"/>
       <c r="M636" t="inlineStr">
         <is>
           <t>Meshmixer;3D Slicer</t>
@@ -44067,8 +43843,6 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr"/>
-      <c r="B637" t="inlineStr"/>
       <c r="C637" t="inlineStr">
         <is>
           <t>A Comparative study on the Effectiveness of Augmented Reality on Denture Tooth Selection.</t>
@@ -44112,7 +43886,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr"/>
       <c r="M637" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -44125,8 +43898,6 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr"/>
-      <c r="B638" t="inlineStr"/>
       <c r="C638" t="inlineStr">
         <is>
           <t>Effect of industrial scanner and framework material interaction on the marginal gaps of CAD-CAM complete arch implant frameworks</t>
@@ -44170,7 +43941,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr">
         <is>
           <t>GOM Inspect;PolyWorks</t>
@@ -44183,8 +43953,6 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr"/>
-      <c r="B639" t="inlineStr"/>
       <c r="C639" t="inlineStr">
         <is>
           <t>Predicting 3D Post-Orthodontic Facial Outcomes With a Diffusion Model Trained on Unpaired Datasets</t>
@@ -44228,7 +43996,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr"/>
       <c r="M639" t="inlineStr">
         <is>
           <t>3D Slicer;CloudCompare</t>
@@ -44241,8 +44008,6 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr"/>
-      <c r="B640" t="inlineStr"/>
       <c r="C640" t="inlineStr">
         <is>
           <t>Intaglio Surface Adaptation of Removable Partial Denture Framework Fabricated by Various Data Acquisition Techniques and Fabrication Approaches.</t>
@@ -44286,7 +44051,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -44299,8 +44063,6 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr"/>
-      <c r="B641" t="inlineStr"/>
       <c r="C641" t="inlineStr">
         <is>
           <t>Modeling fracture in multilayered teeth using the finite volume-based phase field method</t>
@@ -44344,7 +44106,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Wrap;SolidWorks</t>
@@ -44357,8 +44118,6 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr"/>
-      <c r="B642" t="inlineStr"/>
       <c r="C642" t="inlineStr">
         <is>
           <t>Customized 3D-printed models for training in repairing large maxillary sinus membrane perforations.</t>
@@ -44402,7 +44161,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr">
         <is>
           <t>InVesalius</t>
@@ -44415,8 +44173,6 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr"/>
-      <c r="B643" t="inlineStr"/>
       <c r="C643" t="inlineStr">
         <is>
           <t>A Novel Digitized Method for the Design and Additive Manufacturing of Orthodontic Space Maintainers</t>
@@ -44460,7 +44216,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr">
         <is>
           <t>MeshLab;Fusion 360;ANSYS</t>
@@ -44473,8 +44228,6 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr"/>
-      <c r="B644" t="inlineStr"/>
       <c r="C644" t="inlineStr">
         <is>
           <t>Automatic orbital segmentation using deep learning-based 2D U-net and accuracy evaluation: A retrospective study</t>
@@ -44518,7 +44271,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L644" t="inlineStr"/>
       <c r="M644" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -44531,8 +44283,6 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr"/>
-      <c r="B645" t="inlineStr"/>
       <c r="C645" t="inlineStr">
         <is>
           <t>Subtractive versus additive indirect manufacturing techniques of digitally designed partial dentures</t>
@@ -44576,7 +44326,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr"/>
       <c r="M645" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -44589,8 +44338,6 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr"/>
-      <c r="B646" t="inlineStr"/>
       <c r="C646" t="inlineStr">
         <is>
           <t>Validation of a novel tool for automated tooth modelling by fusion of CBCT-derived roots with the respective IOS-derived crowns</t>
@@ -44634,7 +44381,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr">
         <is>
           <t>3-Matic;Mimics</t>
@@ -44647,8 +44393,6 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr"/>
-      <c r="B647" t="inlineStr"/>
       <c r="C647" t="inlineStr">
         <is>
           <t>IDNet: A Diffusion Model-Enhanced Framework for Accurate Cranio-Maxillofacial Bone Defect Repair</t>
@@ -44692,7 +44436,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -44705,8 +44448,6 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr"/>
-      <c r="B648" t="inlineStr"/>
       <c r="C648" t="inlineStr">
         <is>
           <t>Effects of incremental mandibular advancement on upper airways morphology and anatomical structures: a preliminary CT scan study on body donors.</t>
@@ -44750,7 +44491,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -44763,8 +44503,6 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr"/>
-      <c r="B649" t="inlineStr"/>
       <c r="C649" t="inlineStr">
         <is>
           <t>Suitability and Trueness of the Removable Partial Denture Framework Fabricating by Polyether Ether Ketone with CAD-CAM Technology</t>
@@ -44808,7 +44546,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L649" t="inlineStr"/>
       <c r="M649" t="inlineStr">
         <is>
           <t>Geomagic Wrap</t>
@@ -44821,8 +44558,6 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr"/>
-      <c r="B650" t="inlineStr"/>
       <c r="C650" t="inlineStr">
         <is>
           <t>Three-dimensional finite element analysis of full-arch implant-supported dental restorations: complete vs. segmented frameworks</t>
@@ -44866,7 +44601,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L650" t="inlineStr"/>
       <c r="M650" t="inlineStr">
         <is>
           <t>ANSYS Workbench</t>
@@ -44879,8 +44613,6 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr"/>
-      <c r="B651" t="inlineStr"/>
       <c r="C651" t="inlineStr">
         <is>
           <t>Accuracy and surface roughness of Co-Cr partial denture frameworks with different fabrication methods</t>
@@ -44924,7 +44656,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -44937,8 +44668,6 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr"/>
-      <c r="B652" t="inlineStr"/>
       <c r="C652" t="inlineStr">
         <is>
           <t>Three-Dimensional Volumetric Analysis of Frontal Ethmoidal Cells and Evaluation of Influential Factors: A Helical Computed Tomography Study</t>
@@ -44982,7 +44711,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
           <t>InVesalius</t>
@@ -44995,8 +44723,6 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr"/>
-      <c r="B653" t="inlineStr"/>
       <c r="C653" t="inlineStr">
         <is>
           <t>TCFNet: Bidirectional face-bone transformation via a Transformer-based coarse-to-fine point movement network.</t>
@@ -45040,7 +44766,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -45053,8 +44778,6 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr"/>
-      <c r="B654" t="inlineStr"/>
       <c r="C654" t="inlineStr">
         <is>
           <t>DIVA, a 3D virtual reality platform, improves undergraduate craniofacial trauma education</t>
@@ -45098,7 +44821,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr">
         <is>
           <t>Avizo</t>
@@ -45111,8 +44833,6 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr"/>
-      <c r="B655" t="inlineStr"/>
       <c r="C655" t="inlineStr">
         <is>
           <t>The microbiological effect of virgin coconut oil on the morphological and volumetric dimensional changes of 3D printed surgical guides (in vitro study)</t>
@@ -45156,7 +44876,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L655" t="inlineStr"/>
       <c r="M655" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -45169,8 +44888,6 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr"/>
-      <c r="B656" t="inlineStr"/>
       <c r="C656" t="inlineStr">
         <is>
           <t>A novel approach for determining instantaneous centers of rotation of the mandible with an intraoral scanner: A preliminary study.</t>
@@ -45214,7 +44931,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L656" t="inlineStr"/>
       <c r="M656" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -45227,8 +44943,6 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr"/>
-      <c r="B657" t="inlineStr"/>
       <c r="C657" t="inlineStr">
         <is>
           <t>An In Vitro Study of the Reproducibility of the Drilling Access of Digitalized Surgical Guides Generated via Three Different Implant Planning Software Programs</t>
@@ -45272,7 +44986,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L657" t="inlineStr"/>
       <c r="M657" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -45285,8 +44998,6 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr"/>
-      <c r="B658" t="inlineStr"/>
       <c r="C658" t="inlineStr">
         <is>
           <t>Mandible Segmentation of Dental CBCT Scans Affected by Metal Artifacts Using Coarse-to-Fine Learning Model</t>
@@ -45330,7 +45041,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L658" t="inlineStr"/>
       <c r="M658" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -45343,8 +45053,6 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr"/>
-      <c r="B659" t="inlineStr"/>
       <c r="C659" t="inlineStr">
         <is>
           <t>Three-dimensional analysis of mandibular and condylar growth using artificial intelligence tools: a comparison of twin-block and Frankel II Appliances</t>
@@ -45388,7 +45096,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L659" t="inlineStr"/>
       <c r="M659" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -45401,8 +45108,6 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr"/>
-      <c r="B660" t="inlineStr"/>
       <c r="C660" t="inlineStr">
         <is>
           <t>Pressure-based finite element analysis of setup distance in clear aligner canine retraction comparing bodily and tipping movements.</t>
@@ -45446,7 +45151,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L660" t="inlineStr"/>
       <c r="M660" t="inlineStr">
         <is>
           <t>ANSYS</t>
@@ -45459,8 +45163,6 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr"/>
-      <c r="B661" t="inlineStr"/>
       <c r="C661" t="inlineStr">
         <is>
           <t>Computer Aided Orthognathic Surgery: A General Method for Designing and Manufacturing Personalized Cutting/Repositioning Templates</t>
@@ -45504,7 +45206,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr">
         <is>
           <t>3D Slicer;Geomagic Design X;Rhinoceros</t>
@@ -45517,8 +45218,6 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr"/>
-      <c r="B662" t="inlineStr"/>
       <c r="C662" t="inlineStr">
         <is>
           <t>A Comparison of Denture Base Retention and Adaptation Between CAD/CAM and Conventional Fabrication Techniques</t>
@@ -45562,7 +45261,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr">
         <is>
           <t>Meshmixer;Geomagic Control X</t>
@@ -45575,8 +45273,6 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr"/>
-      <c r="B663" t="inlineStr"/>
       <c r="C663" t="inlineStr">
         <is>
           <t>Mechanical Performance of Chairside Ceramic CAD/CAM Restorations and Zirconia Abutments with Different Internal Implant Connections: In Vitro Study and Finite Element Analysis</t>
@@ -45620,7 +45316,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr"/>
       <c r="M663" t="inlineStr">
         <is>
           <t>SolidWorks;ANSYS Workbench</t>
@@ -45633,8 +45328,6 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr"/>
-      <c r="B664" t="inlineStr"/>
       <c r="C664" t="inlineStr">
         <is>
           <t>Stress distribution in titanium and zirconia implants with full-arch prostheses: a finite element analysis.</t>
@@ -45678,7 +45371,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr"/>
       <c r="M664" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;HyperMesh;ALTAIR OptiStruct</t>
@@ -45691,8 +45383,6 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr"/>
-      <c r="B665" t="inlineStr"/>
       <c r="C665" t="inlineStr">
         <is>
           <t>Comparative analysis of five AI platforms for mandibular canal segmentation on CBCT images</t>
@@ -45736,7 +45426,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr"/>
       <c r="M665" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -45749,8 +45438,6 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr"/>
-      <c r="B666" t="inlineStr"/>
       <c r="C666" t="inlineStr">
         <is>
           <t>Study on fracture behavior of molars based on three-dimensional high-precision computerized tomography scanning and numerical simulation</t>
@@ -45794,7 +45481,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr">
         <is>
           <t>Avizo</t>
@@ -45807,8 +45493,6 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr"/>
-      <c r="B667" t="inlineStr"/>
       <c r="C667" t="inlineStr">
         <is>
           <t>Clinical implementation of an EU MDR-compliant point-of-care manufacturing framework for patient-specific 3D-printed PEEK implants in craniomaxillofacial  reconstruction.</t>
@@ -45852,7 +45536,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Freeform</t>
@@ -45865,8 +45548,6 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr"/>
-      <c r="B668" t="inlineStr"/>
       <c r="C668" t="inlineStr">
         <is>
           <t>Robot-assisted augmented reality navigation for osteotomy and personalized guide-plate in mandibular reconstruction: a preclinical study</t>
@@ -45910,7 +45591,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr">
         <is>
           <t>3-Matic</t>
@@ -45923,8 +45603,6 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr"/>
-      <c r="B669" t="inlineStr"/>
       <c r="C669" t="inlineStr">
         <is>
           <t>The accuracy of a novel image-guided hybrid robotic system for dental implant placement: An in vitro study.</t>
@@ -45968,7 +45646,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L669" t="inlineStr"/>
       <c r="M669" t="inlineStr">
         <is>
           <t>Geomagic Studio;Brainlab CMF</t>
@@ -45981,8 +45658,6 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr"/>
-      <c r="B670" t="inlineStr"/>
       <c r="C670" t="inlineStr">
         <is>
           <t>AI-Assisted Identification of the Medial Lingual Foramen on CBCT: A Deep Learning Approach for Preoperative Implant Assessment.</t>
@@ -46026,7 +45701,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -46039,8 +45713,6 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr"/>
-      <c r="B671" t="inlineStr"/>
       <c r="C671" t="inlineStr">
         <is>
           <t>Oral-Anatomical Knowledge-Informed Semi-Supervised Learning for 3D Dental CBCT Segmentation and Lesion Detection</t>
@@ -46084,7 +45756,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L671" t="inlineStr"/>
       <c r="M671" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -46097,8 +45768,6 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr"/>
-      <c r="B672" t="inlineStr"/>
       <c r="C672" t="inlineStr">
         <is>
           <t>Workflow for guided implant placement based on anatomic landmarks and the CAD-CAM fabrication of a prosthetic framework for an implant-supported fixed dental prosthesis</t>
@@ -46142,7 +45811,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr"/>
       <c r="M672" t="inlineStr">
         <is>
           <t>Mimics;3D Slicer;InVesalius;SpaceClaim</t>
@@ -46155,8 +45823,6 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr"/>
-      <c r="B673" t="inlineStr"/>
       <c r="C673" t="inlineStr">
         <is>
           <t>STRESS DISTRIBUTION OF MONOLITHIC AND VENEERED THREE-UNIT ZIRCONIA FDPS: A FINITE ELEMENT ANALYSIS</t>
@@ -46200,7 +45866,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr"/>
       <c r="M673" t="inlineStr">
         <is>
           <t>ANSYS;SpaceClaim</t>
@@ -46213,8 +45878,6 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr"/>
-      <c r="B674" t="inlineStr"/>
       <c r="C674" t="inlineStr">
         <is>
           <t>Combining Coaxial Electrospinning and 3D Printing: Design of Biodegradable Bilayered Membranes with Dual Drug Delivery Capability for Periodontitis  Treatment.</t>
@@ -46258,7 +45921,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr"/>
       <c r="M674" t="inlineStr">
         <is>
           <t>Cura</t>
@@ -46271,8 +45933,6 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr"/>
-      <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr">
         <is>
           <t>Skeletal facial asymmetry: reliability of manual and artificial intelligence-driven analysis</t>
@@ -46316,7 +45976,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L675" t="inlineStr"/>
       <c r="M675" t="inlineStr">
         <is>
           <t>OsiriX</t>
@@ -46329,8 +45988,6 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr"/>
-      <c r="B676" t="inlineStr"/>
       <c r="C676" t="inlineStr">
         <is>
           <t>A novel fluoride tray-assisted workflow for artificial intelligence-driven automated maxillary gingival segmentation on cone beam CT</t>
@@ -46374,7 +46031,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L676" t="inlineStr"/>
       <c r="M676" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -46387,8 +46043,6 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr"/>
-      <c r="B677" t="inlineStr"/>
       <c r="C677" t="inlineStr">
         <is>
           <t>Reduced graphene oxide loaded with tetrahedral framework nucleic acids for combating orthodontically induced root resorption</t>
@@ -46432,7 +46086,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr"/>
       <c r="M677" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Wrap</t>
@@ -46445,8 +46098,6 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr"/>
-      <c r="B678" t="inlineStr"/>
       <c r="C678" t="inlineStr">
         <is>
           <t>Jaw Morphology and Factors Associated with Upper Impacted Canines: Case-Controlled Trial</t>
@@ -46490,7 +46141,6 @@
           <t>Morphological and Phenotypic Analysis</t>
         </is>
       </c>
-      <c r="L678" t="inlineStr"/>
       <c r="M678" t="inlineStr">
         <is>
           <t>RapidForm</t>
@@ -46503,8 +46153,6 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr"/>
-      <c r="B679" t="inlineStr"/>
       <c r="C679" t="inlineStr">
         <is>
           <t>Low-Profile Electromagnetic Field Sensors in the Measurement and Modelling of Three-Dimensional Jaw Kinematics and Occlusal Loading</t>
@@ -46548,7 +46196,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L679" t="inlineStr"/>
       <c r="M679" t="inlineStr">
         <is>
           <t>3-Matic;ABAQUS</t>
@@ -46561,8 +46208,6 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr"/>
-      <c r="B680" t="inlineStr"/>
       <c r="C680" t="inlineStr">
         <is>
           <t>Digital Dental Biometrics for Human Identification Based on Automated 3D Point Cloud Feature Extraction and Registration</t>
@@ -46606,7 +46251,6 @@
           <t>Morphological and Phenotypic Analysis</t>
         </is>
       </c>
-      <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr">
         <is>
           <t>MeshLab;CloudCompare</t>
@@ -46619,8 +46263,6 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr"/>
-      <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr">
         <is>
           <t>Fully Digital versus Conventional Workflows for Fabricating Posterior Three-Unit Implant-Supported Reconstructions: A Prospective Crossover Clinical Trial</t>
@@ -46664,7 +46306,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L681" t="inlineStr"/>
       <c r="M681" t="inlineStr">
         <is>
           <t>GOM Inspect;AutoCAD</t>
@@ -46677,8 +46318,6 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr"/>
-      <c r="B682" t="inlineStr"/>
       <c r="C682" t="inlineStr">
         <is>
           <t>In Vivo Assessment of SED: A Novel Biomechanical Indicator for Periodontal Tissue Remodeling in Clear Aligner Therapy</t>
@@ -46722,7 +46361,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Studio;Siemens NX (UG);ANSYS Workbench</t>
@@ -46735,8 +46373,6 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr"/>
-      <c r="B683" t="inlineStr"/>
       <c r="C683" t="inlineStr">
         <is>
           <t>3D printing titanium grid scaffold facilitates osteogenesis in mandibular segmental defects</t>
@@ -46780,7 +46416,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr"/>
       <c r="M683" t="inlineStr">
         <is>
           <t>3-Matic</t>
@@ -46793,8 +46428,6 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr"/>
-      <c r="B684" t="inlineStr"/>
       <c r="C684" t="inlineStr">
         <is>
           <t>3D printed indirect bonding trays: transfer accuracy of bar vs shell design in a prospective, randomized clinical trial</t>
@@ -46838,7 +46471,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L684" t="inlineStr"/>
       <c r="M684" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -46851,8 +46483,6 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr"/>
-      <c r="B685" t="inlineStr"/>
       <c r="C685" t="inlineStr">
         <is>
           <t>Computational Evaluation of Stress Distribution in Endocrown-Restored Immature Mandibular Molars: A Finite Element Approach</t>
@@ -46896,7 +46526,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L685" t="inlineStr"/>
       <c r="M685" t="inlineStr">
         <is>
           <t>HyperMesh;ALTAIR OptiStruct</t>
@@ -46909,8 +46538,6 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr"/>
-      <c r="B686" t="inlineStr"/>
       <c r="C686" t="inlineStr">
         <is>
           <t>Effect of Internal Structural Design on Stress Distribution in 3D-Printed Subperiosteal Implants Under Mechanical Loading</t>
@@ -46954,7 +46581,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L686" t="inlineStr"/>
       <c r="M686" t="inlineStr">
         <is>
           <t>ABAQUS;VGStudio MAX</t>
@@ -46967,8 +46593,6 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr"/>
-      <c r="B687" t="inlineStr"/>
       <c r="C687" t="inlineStr">
         <is>
           <t>Mandibular stability and condylar changes following orthognathic surgery in mandibular hypoplasia patients associated with preoperative condylar resorption</t>
@@ -47012,7 +46636,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L687" t="inlineStr"/>
       <c r="M687" t="inlineStr">
         <is>
           <t>Geomagic Studio</t>
@@ -47025,8 +46648,6 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr"/>
-      <c r="B688" t="inlineStr"/>
       <c r="C688" t="inlineStr">
         <is>
           <t>Procedure Increasing the Accuracy of Modelling and the Manufacturing of Surgical Templates with the Use of 3D Printing Techniques, Applied in Planning the Procedures of Reconstruction of the Mandible</t>
@@ -47070,7 +46691,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L688" t="inlineStr"/>
       <c r="M688" t="inlineStr">
         <is>
           <t>Geomagic (unspecified);GOM Inspect</t>
@@ -47083,8 +46703,6 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr"/>
-      <c r="B689" t="inlineStr"/>
       <c r="C689" t="inlineStr">
         <is>
           <t>Mandibular extracellular vesicles mediate morphogenesis and mineralization of tooth germs in miniature swine through the miR-206/HDAC4 signaling axis</t>
@@ -47128,7 +46746,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L689" t="inlineStr"/>
       <c r="M689" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -47141,8 +46758,6 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="inlineStr"/>
-      <c r="B690" t="inlineStr"/>
       <c r="C690" t="inlineStr">
         <is>
           <t>Digital assessment of the accuracy of implant impression techniques in free end saddle partially edentulous patients. A controlled clinical trial</t>
@@ -47186,7 +46801,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L690" t="inlineStr"/>
       <c r="M690" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -47199,8 +46813,6 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="inlineStr"/>
-      <c r="B691" t="inlineStr"/>
       <c r="C691" t="inlineStr">
         <is>
           <t>A Digital Workflow for the Fabrication of a Milled Removable Partial Denture</t>
@@ -47244,7 +46856,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -47257,8 +46868,6 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="inlineStr"/>
-      <c r="B692" t="inlineStr"/>
       <c r="C692" t="inlineStr">
         <is>
           <t>Patient-specific virtual surgical planning for tongue reconstruction: evaluating hyperelastic inverse FEM with four simulated tongue cancer cases</t>
@@ -47302,7 +46911,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr">
         <is>
           <t>Mimics;Meshmixer</t>
@@ -47315,8 +46923,6 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="inlineStr"/>
-      <c r="B693" t="inlineStr"/>
       <c r="C693" t="inlineStr">
         <is>
           <t>Posterior implant angulation without cantilever reduction in mandibular All-on-4: a controlled finite element analysis of stress transfer and implant macrodesign  effects.</t>
@@ -47360,7 +46966,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L693" t="inlineStr"/>
       <c r="M693" t="inlineStr">
         <is>
           <t>Rhinoceros;3D-DOCTOR;ALGOR</t>
@@ -47373,8 +46978,6 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="inlineStr"/>
-      <c r="B694" t="inlineStr"/>
       <c r="C694" t="inlineStr">
         <is>
           <t>Multi-view deep learning for mandibular landmark localization</t>
@@ -47418,7 +47021,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L694" t="inlineStr"/>
       <c r="M694" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Wrap</t>
@@ -47431,8 +47033,6 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="inlineStr"/>
-      <c r="B695" t="inlineStr"/>
       <c r="C695" t="inlineStr">
         <is>
           <t>Three-Dimensional Finite Element Analysis of Stress Distribution in a Tooth Restored with Full Coverage Machined Polymer Crown</t>
@@ -47476,7 +47076,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr">
         <is>
           <t>Mimics;HyperMesh</t>
@@ -47489,8 +47088,6 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="inlineStr"/>
-      <c r="B696" t="inlineStr"/>
       <c r="C696" t="inlineStr">
         <is>
           <t>Comparing the trueness of 3D printing and conventional casting for removable partial denture metal framework fabrication in different mandibular major connectors designs: An in vitro study</t>
@@ -47534,7 +47131,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -47547,8 +47143,6 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" t="inlineStr"/>
-      <c r="B697" t="inlineStr"/>
       <c r="C697" t="inlineStr">
         <is>
           <t>Direct ink writing with dental composites: A paradigm shift toward sustainable chair-side production</t>
@@ -47592,7 +47186,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr">
         <is>
           <t>CloudCompare;Cura</t>
@@ -47605,8 +47198,6 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" t="inlineStr"/>
-      <c r="B698" t="inlineStr"/>
       <c r="C698" t="inlineStr">
         <is>
           <t>Automated artificial intelligence-driven 3-dimensional craniofacial superimposition for clinically useful treatment outcomes in growing patients: A  multicenter study.</t>
@@ -47650,7 +47241,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr">
         <is>
           <t>ITK-SNAP;3D Slicer</t>
@@ -47663,8 +47253,6 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" t="inlineStr"/>
-      <c r="B699" t="inlineStr"/>
       <c r="C699" t="inlineStr">
         <is>
           <t>Microstructure and Mechanical Properties of Co-Cr Alloy Fabricated by Selective Laser Melting Technology for Removable Partial Denture Frameworks</t>
@@ -47708,7 +47296,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L699" t="inlineStr"/>
       <c r="M699" t="inlineStr">
         <is>
           <t>Siemens NX (UG)</t>
@@ -47721,8 +47308,6 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" t="inlineStr"/>
-      <c r="B700" t="inlineStr"/>
       <c r="C700" t="inlineStr">
         <is>
           <t>A Three-Year Prospective Study Comparing Stereolithography Printed Models to Classical Impression and Plaster Cast Models in Orthodontic Therapy: A 3D Objectification Approach</t>
@@ -47766,7 +47351,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L700" t="inlineStr"/>
       <c r="M700" t="inlineStr">
         <is>
           <t>Meshmixer;CloudCompare</t>
@@ -47779,8 +47363,6 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" t="inlineStr"/>
-      <c r="B701" t="inlineStr"/>
       <c r="C701" t="inlineStr">
         <is>
           <t>Comparison of marginal accuracy in two different materials used in provisional crown and bridge - an in vitro experimental study</t>
@@ -47824,7 +47406,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr"/>
       <c r="M701" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -47837,8 +47418,6 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="inlineStr"/>
-      <c r="B702" t="inlineStr"/>
       <c r="C702" t="inlineStr">
         <is>
           <t>Biomimetic 3D-printed gyroid scaffolds with versatile bioactive coatings for complex craniomaxillofacial bone regeneration</t>
@@ -47882,7 +47461,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr"/>
       <c r="M702" t="inlineStr">
         <is>
           <t>Geomagic Freeform;3-Matic</t>
@@ -47895,8 +47473,6 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="inlineStr"/>
-      <c r="B703" t="inlineStr"/>
       <c r="C703" t="inlineStr">
         <is>
           <t>Intelligent geometry compensation for additive manufactured oral maxillary stent by genetic algorithm and backpropagation network</t>
@@ -47940,7 +47516,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L703" t="inlineStr"/>
       <c r="M703" t="inlineStr">
         <is>
           <t>Magics;Geomagic Wrap</t>
@@ -47953,8 +47528,6 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="inlineStr"/>
-      <c r="B704" t="inlineStr"/>
       <c r="C704" t="inlineStr">
         <is>
           <t>Geometric plane alignment as a methodological requirement for accurate angular measurement in three-dimensional craniofacial imaging.</t>
@@ -47998,7 +47571,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L704" t="inlineStr"/>
       <c r="M704" t="inlineStr">
         <is>
           <t>Horos</t>
@@ -48011,14 +47583,11 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" t="inlineStr"/>
-      <c r="B705" t="inlineStr"/>
       <c r="C705" t="inlineStr">
         <is>
           <t>Accuracy of guided implant surgery obtained using 3D-printed surgical guides - An in vitro comparison of four evaluation methods</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
       <c r="E705" t="inlineStr">
         <is>
           <t>Int J Comput Dent</t>
@@ -48052,7 +47621,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L705" t="inlineStr"/>
       <c r="M705" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -48065,8 +47633,6 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="inlineStr"/>
-      <c r="B706" t="inlineStr"/>
       <c r="C706" t="inlineStr">
         <is>
           <t>Effect of framework material and gyroid lattice design on the biomechanics of all-on-four full-arch prostheses.</t>
@@ -48110,7 +47676,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L706" t="inlineStr"/>
       <c r="M706" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;HyperMesh</t>
@@ -48123,8 +47688,6 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" t="inlineStr"/>
-      <c r="B707" t="inlineStr"/>
       <c r="C707" t="inlineStr">
         <is>
           <t>In vivo trueness and precision of full-arch implant scans using intraoral scanners with three different acquisition protocols</t>
@@ -48168,7 +47731,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L707" t="inlineStr"/>
       <c r="M707" t="inlineStr">
         <is>
           <t>Geomagic Design X;Geomagic Control X</t>
@@ -48181,8 +47743,6 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="inlineStr"/>
-      <c r="B708" t="inlineStr"/>
       <c r="C708" t="inlineStr">
         <is>
           <t>Prosthesis repair of oral implants based on artificial intelligenc`e finite element analysis</t>
@@ -48226,7 +47786,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L708" t="inlineStr"/>
       <c r="M708" t="inlineStr">
         <is>
           <t>Mimics;ANSYS</t>
@@ -48239,8 +47798,6 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" t="inlineStr"/>
-      <c r="B709" t="inlineStr"/>
       <c r="C709" t="inlineStr">
         <is>
           <t>Hierarchical 2D to 3D micro/nano-histology of human dental caries lesions using light, X-ray and electron microscopy</t>
@@ -48284,7 +47841,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L709" t="inlineStr"/>
       <c r="M709" t="inlineStr">
         <is>
           <t>Avizo</t>
@@ -48297,8 +47853,6 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" t="inlineStr"/>
-      <c r="B710" t="inlineStr"/>
       <c r="C710" t="inlineStr">
         <is>
           <t>Study on 3D printed MXene-berberine-integrated scaffold for photo-activated antibacterial activity and bone regeneration</t>
@@ -48342,7 +47896,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L710" t="inlineStr"/>
       <c r="M710" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -48355,8 +47908,6 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" t="inlineStr"/>
-      <c r="B711" t="inlineStr"/>
       <c r="C711" t="inlineStr">
         <is>
           <t>Multi-Architecture deep learning for CBCT segmentation of dental hard tissues and pulp in mixed dentition.</t>
@@ -48400,7 +47951,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L711" t="inlineStr"/>
       <c r="M711" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -48413,8 +47963,6 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="inlineStr"/>
-      <c r="B712" t="inlineStr"/>
       <c r="C712" t="inlineStr">
         <is>
           <t>Protease-responsive protein hydrogel enabling spatiotemporal ClO2 release for precision treatment of intracellular infections and periodontitis</t>
@@ -48458,7 +48006,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L712" t="inlineStr"/>
       <c r="M712" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -48471,8 +48018,6 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="inlineStr"/>
-      <c r="B713" t="inlineStr"/>
       <c r="C713" t="inlineStr">
         <is>
           <t>Impact of framework material, cantilever design, and wing configuration on stress distribution in patient specific additively manufactured subperiosteal jaw implants: a 3D finite element analysis</t>
@@ -48516,7 +48061,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L713" t="inlineStr"/>
       <c r="M713" t="inlineStr">
         <is>
           <t>3D Slicer;SpaceClaim;ANSYS Workbench;LS-DYNA;Rhinoceros;VRMesh</t>
@@ -48529,8 +48073,6 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="inlineStr"/>
-      <c r="B714" t="inlineStr"/>
       <c r="C714" t="inlineStr">
         <is>
           <t>Effect of print orientation of 3D-printed aligner templates on the volumetric accuracy of transferred composite attachments: an in vitro study</t>
@@ -48574,7 +48116,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L714" t="inlineStr"/>
       <c r="M714" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -48587,8 +48128,6 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" t="inlineStr"/>
-      <c r="B715" t="inlineStr"/>
       <c r="C715" t="inlineStr">
         <is>
           <t>Comparison of stereolithography (STL) and polygon file format (PLY) for intraoral scans: From chairside to archive.</t>
@@ -48632,7 +48171,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L715" t="inlineStr"/>
       <c r="M715" t="inlineStr">
         <is>
           <t>Blender;MeshLab</t>
@@ -48645,8 +48183,6 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" t="inlineStr"/>
-      <c r="B716" t="inlineStr"/>
       <c r="C716" t="inlineStr">
         <is>
           <t>Spatiotemporal mechanical stimuli from dental crypt during tooth development: An integrated experimental and computational study</t>
@@ -48690,7 +48226,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L716" t="inlineStr"/>
       <c r="M716" t="inlineStr">
         <is>
           <t>Avizo;ABAQUS</t>
@@ -48703,8 +48238,6 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="inlineStr"/>
-      <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr">
         <is>
           <t>Etched 3D-Printed Polycaprolactone Constructs Functionalized with Reduced Graphene Oxide for Enhanced Attachment of Dental Pulp-Derived Stem Cells</t>
@@ -48748,7 +48281,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L717" t="inlineStr"/>
       <c r="M717" t="inlineStr">
         <is>
           <t>Inventor</t>
@@ -48761,8 +48293,6 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" t="inlineStr"/>
-      <c r="B718" t="inlineStr"/>
       <c r="C718" t="inlineStr">
         <is>
           <t>Impact of the superimposition reference area on intraoral scanning accuracy in a partially dentate maxilla.</t>
@@ -48806,7 +48336,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L718" t="inlineStr"/>
       <c r="M718" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -48819,8 +48348,6 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="inlineStr"/>
-      <c r="B719" t="inlineStr"/>
       <c r="C719" t="inlineStr">
         <is>
           <t>A customised 3D U-Net model for bifid mandibular canal segmentation and detection on CBCT: a diagnostic accuracy study</t>
@@ -48864,7 +48391,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L719" t="inlineStr"/>
       <c r="M719" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -48877,8 +48403,6 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" t="inlineStr"/>
-      <c r="B720" t="inlineStr"/>
       <c r="C720" t="inlineStr">
         <is>
           <t>Clinical efficacy of early intervention timing for inversely impacted maxillary central incisors</t>
@@ -48922,7 +48446,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L720" t="inlineStr"/>
       <c r="M720" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -48935,8 +48458,6 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" t="inlineStr"/>
-      <c r="B721" t="inlineStr"/>
       <c r="C721" t="inlineStr">
         <is>
           <t>Impact of profile angle of CAD-CAM abutment on the marginal bone loss of implant-supported single-tooth posterior restorations</t>
@@ -48980,7 +48501,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L721" t="inlineStr"/>
       <c r="M721" t="inlineStr">
         <is>
           <t>AutoCAD</t>
@@ -48993,8 +48513,6 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="inlineStr"/>
-      <c r="B722" t="inlineStr"/>
       <c r="C722" t="inlineStr">
         <is>
           <t>Biomechanical evaluation of prosthetic framework materials in subperiosteal implants: a finite element analysis</t>
@@ -49038,7 +48556,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L722" t="inlineStr"/>
       <c r="M722" t="inlineStr">
         <is>
           <t>Mimics;SolidWorks;SpaceClaim;ANSYS Workbench</t>
@@ -49051,8 +48568,6 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" t="inlineStr"/>
-      <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr">
         <is>
           <t>A 3D In-vitro model of the human dentine interface shows long-range osteoinduction from the dentine surface</t>
@@ -49096,7 +48611,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L723" t="inlineStr"/>
       <c r="M723" t="inlineStr">
         <is>
           <t>Inventor</t>
@@ -49109,8 +48623,6 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" t="inlineStr"/>
-      <c r="B724" t="inlineStr"/>
       <c r="C724" t="inlineStr">
         <is>
           <t>AI-driven automation of occlusal surface design in digital prosthodontics: a clinically validated workflow</t>
@@ -49154,7 +48666,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L724" t="inlineStr"/>
       <c r="M724" t="inlineStr">
         <is>
           <t>3-Matic</t>
@@ -49167,8 +48678,6 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" t="inlineStr"/>
-      <c r="B725" t="inlineStr"/>
       <c r="C725" t="inlineStr">
         <is>
           <t>Detecting Mandible Fractures in CBCT Scans Using a 3-Stage Neural Network.</t>
@@ -49212,7 +48721,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L725" t="inlineStr"/>
       <c r="M725" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -49225,8 +48733,6 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" t="inlineStr"/>
-      <c r="B726" t="inlineStr"/>
       <c r="C726" t="inlineStr">
         <is>
           <t>Digital model superimpositions: are different software algorithms equally accurate in quantifying linear tooth movements?</t>
@@ -49270,7 +48776,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L726" t="inlineStr"/>
       <c r="M726" t="inlineStr">
         <is>
           <t>Geomagic (unspecified)</t>
@@ -49283,8 +48788,6 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" t="inlineStr"/>
-      <c r="B727" t="inlineStr"/>
       <c r="C727" t="inlineStr">
         <is>
           <t>Accuracy of face scan-based virtual facebow records: A comparison between two registration methods</t>
@@ -49328,7 +48831,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L727" t="inlineStr"/>
       <c r="M727" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -49341,8 +48843,6 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" t="inlineStr"/>
-      <c r="B728" t="inlineStr"/>
       <c r="C728" t="inlineStr">
         <is>
           <t>Microrobotics for Precision Biofilm Diagnostics and Treatment</t>
@@ -49386,7 +48886,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L728" t="inlineStr"/>
       <c r="M728" t="inlineStr">
         <is>
           <t>SolidWorks</t>
@@ -49399,8 +48898,6 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" t="inlineStr"/>
-      <c r="B729" t="inlineStr"/>
       <c r="C729" t="inlineStr">
         <is>
           <t>Passive fit and time efficiency for prefabricated versus conventionally constructed cobalt chromium CAD\textbackslashCAM 3-unit implant supported frameworks in free end saddle models: a pilot invitro study</t>
@@ -49444,7 +48941,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L729" t="inlineStr"/>
       <c r="M729" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -49457,8 +48953,6 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="inlineStr"/>
-      <c r="B730" t="inlineStr"/>
       <c r="C730" t="inlineStr">
         <is>
           <t>Effect of different storage conditions on dimensional accuracy of 3D-printed dental models</t>
@@ -49502,7 +48996,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L730" t="inlineStr"/>
       <c r="M730" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -49515,8 +49008,6 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" t="inlineStr"/>
-      <c r="B731" t="inlineStr"/>
       <c r="C731" t="inlineStr">
         <is>
           <t>Mechanotherapeutic Modulation of the Nasal Microenvironment: RAMPA-Induced Maxillofacial Remodeling and Its Pathophysiological Impact on Mucus Rheology and  Chronic Inflammation.</t>
@@ -49560,7 +49051,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L731" t="inlineStr"/>
       <c r="M731" t="inlineStr">
         <is>
           <t>ANSYS Workbench;Mimics</t>
@@ -49573,8 +49063,6 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" t="inlineStr"/>
-      <c r="B732" t="inlineStr"/>
       <c r="C732" t="inlineStr">
         <is>
           <t>Comparison of Low-Dose, Standard-Dose, and High-Definition CBCT Protocols for STL Reconstruction Accuracy in Digital Bone Scaffold Workflows.</t>
@@ -49618,7 +49106,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L732" t="inlineStr"/>
       <c r="M732" t="inlineStr">
         <is>
           <t>3D Slicer;CloudCompare</t>
@@ -49631,8 +49118,6 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" t="inlineStr"/>
-      <c r="B733" t="inlineStr"/>
       <c r="C733" t="inlineStr">
         <is>
           <t>Feasibility of augmented reality using dental arch-based registration applied to navigation in mandibular distraction osteogenesis: a phantom experiment</t>
@@ -49676,7 +49161,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L733" t="inlineStr"/>
       <c r="M733" t="inlineStr">
         <is>
           <t>3-Matic;Mimics</t>
@@ -49689,8 +49173,6 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" t="inlineStr"/>
-      <c r="B734" t="inlineStr"/>
       <c r="C734" t="inlineStr">
         <is>
           <t>Automatic prediction of depth of invasion in oral tongue squamous cell carcinoma using a multimodal regression network fusing prior text and anatomical knowledge</t>
@@ -49734,7 +49216,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L734" t="inlineStr"/>
       <c r="M734" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -49747,8 +49228,6 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" t="inlineStr"/>
-      <c r="B735" t="inlineStr"/>
       <c r="C735" t="inlineStr">
         <is>
           <t>Comparison of biomechanical performance of custom implants with different designs under functional load: a finite element analysis.</t>
@@ -49792,7 +49271,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L735" t="inlineStr"/>
       <c r="M735" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;HyperMesh;ALTAIR OptiStruct</t>
@@ -49805,8 +49283,6 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" t="inlineStr"/>
-      <c r="B736" t="inlineStr"/>
       <c r="C736" t="inlineStr">
         <is>
           <t>Development and Validation of a Freehand 3-D Ultrasound System for Real-Time Intraoral Image Reconstruction</t>
@@ -49850,7 +49326,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L736" t="inlineStr"/>
       <c r="M736" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -49863,8 +49338,6 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" t="inlineStr"/>
-      <c r="B737" t="inlineStr"/>
       <c r="C737" t="inlineStr">
         <is>
           <t>In-vivo evaluation of Artificial Intelligence Driven Remote Monitoring technology for tracking tooth movement and reconstruction of 3-dimensional digital models during orthodontic treatment</t>
@@ -49908,7 +49381,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L737" t="inlineStr"/>
       <c r="M737" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -49921,8 +49393,6 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" t="inlineStr"/>
-      <c r="B738" t="inlineStr"/>
       <c r="C738" t="inlineStr">
         <is>
           <t>Biomechanical Evaluation of Framework Materials in All-on-Four Versus All-on-Six Prostheses: A Finite Element Study.</t>
@@ -49966,7 +49436,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L738" t="inlineStr"/>
       <c r="M738" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Design X;SolidWorks;ABAQUS</t>
@@ -49979,8 +49448,6 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" t="inlineStr"/>
-      <c r="B739" t="inlineStr"/>
       <c r="C739" t="inlineStr">
         <is>
           <t>Biomechanics of the tooth cervical region investigated using 3D digital image correlation, micro CT, and finite element analysis</t>
@@ -50024,7 +49491,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L739" t="inlineStr"/>
       <c r="M739" t="inlineStr">
         <is>
           <t>Amira;Blender;FreeCAD</t>
@@ -50037,8 +49503,6 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" t="inlineStr"/>
-      <c r="B740" t="inlineStr"/>
       <c r="C740" t="inlineStr">
         <is>
           <t>A Low-Cost Wireless Bite Force Measurement Device</t>
@@ -50082,7 +49546,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L740" t="inlineStr"/>
       <c r="M740" t="inlineStr">
         <is>
           <t>AutoCAD</t>
@@ -50095,8 +49558,6 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" t="inlineStr"/>
-      <c r="B741" t="inlineStr"/>
       <c r="C741" t="inlineStr">
         <is>
           <t>Comparison of the accuracy of removable partial denture frameworks fabricated using conventional and digital impressions: a clinical study</t>
@@ -50140,7 +49601,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L741" t="inlineStr"/>
       <c r="M741" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -50153,8 +49613,6 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="inlineStr"/>
-      <c r="B742" t="inlineStr"/>
       <c r="C742" t="inlineStr">
         <is>
           <t>Biomechanical comparison of titanium and Y-TZP subperiosteal implants in atrophic maxilla: a finite element study.</t>
@@ -50198,7 +49656,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L742" t="inlineStr"/>
       <c r="M742" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;HyperMesh</t>
@@ -50211,8 +49668,6 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" t="inlineStr"/>
-      <c r="B743" t="inlineStr"/>
       <c r="C743" t="inlineStr">
         <is>
           <t>Effect of attachment flash on clear aligner force delivery: an in vitro study</t>
@@ -50256,7 +49711,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L743" t="inlineStr"/>
       <c r="M743" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -50269,8 +49723,6 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="inlineStr"/>
-      <c r="B744" t="inlineStr"/>
       <c r="C744" t="inlineStr">
         <is>
           <t>Evaluation of the stability of the palatal rugae using the three-dimensional orthodontic treatment</t>
@@ -50314,7 +49766,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L744" t="inlineStr"/>
       <c r="M744" t="inlineStr">
         <is>
           <t>Geomagic Studio</t>
@@ -50327,8 +49778,6 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" t="inlineStr"/>
-      <c r="B745" t="inlineStr"/>
       <c r="C745" t="inlineStr">
         <is>
           <t>Evaluation of an AI-based segmentation model for mandibular fracture segmentation on CBCT using volumetric and 2D slice-based validation approaches.</t>
@@ -50372,7 +49821,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L745" t="inlineStr"/>
       <c r="M745" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -50385,8 +49833,6 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" t="inlineStr"/>
-      <c r="B746" t="inlineStr"/>
       <c r="C746" t="inlineStr">
         <is>
           <t>Comparison of the reproducibility of maxillary position transfer with a mechanical facebow and those with facial scanning and cone beam computed  tomography, based on a method of model orientation using anatomical landmarks.</t>
@@ -50430,7 +49876,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L746" t="inlineStr"/>
       <c r="M746" t="inlineStr">
         <is>
           <t>Geomagic Control X;Mimics;Geomagic Wrap</t>
@@ -50443,8 +49888,6 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" t="inlineStr"/>
-      <c r="B747" t="inlineStr"/>
       <c r="C747" t="inlineStr">
         <is>
           <t>Does adding markers increase the accuracy and efficiency of intraoral scanning of complete dentures?</t>
@@ -50488,7 +49931,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L747" t="inlineStr"/>
       <c r="M747" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -50501,8 +49943,6 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" t="inlineStr"/>
-      <c r="B748" t="inlineStr"/>
       <c r="C748" t="inlineStr">
         <is>
           <t>A finite element analysis of a dental implant with a conformal lattice structure: a parametric exploration under occlusal loading.</t>
@@ -50546,7 +49986,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L748" t="inlineStr"/>
       <c r="M748" t="inlineStr">
         <is>
           <t>ANSYS Workbench</t>
@@ -50559,8 +49998,6 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" t="inlineStr"/>
-      <c r="B749" t="inlineStr"/>
       <c r="C749" t="inlineStr">
         <is>
           <t>Evaluation of the accuracy (trueness, precision) and processing time of different 3-dimensional CAD software programs and algorithms for virtual cast alignment.</t>
@@ -50604,7 +50041,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L749" t="inlineStr"/>
       <c r="M749" t="inlineStr">
         <is>
           <t>Blender;Meshmixer</t>
@@ -50617,8 +50053,6 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" t="inlineStr"/>
-      <c r="B750" t="inlineStr"/>
       <c r="C750" t="inlineStr">
         <is>
           <t>Three-Dimensional Printed Hydroxyapatite Bone Substitutes Designed by a Novel Periodic Minimal Surface Algorithm Are Highly Osteoconductive</t>
@@ -50662,7 +50096,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L750" t="inlineStr"/>
       <c r="M750" t="inlineStr">
         <is>
           <t>Magics</t>
@@ -50675,8 +50108,6 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" t="inlineStr"/>
-      <c r="B751" t="inlineStr"/>
       <c r="C751" t="inlineStr">
         <is>
           <t>Deep learning driven segmentation of maxillary impacted canine on cone beam computed tomography images</t>
@@ -50720,7 +50151,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L751" t="inlineStr"/>
       <c r="M751" t="inlineStr">
         <is>
           <t>3-Matic</t>
@@ -50733,8 +50163,6 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" t="inlineStr"/>
-      <c r="B752" t="inlineStr"/>
       <c r="C752" t="inlineStr">
         <is>
           <t>A comparative study of bone remodeling around hydroxyapatite-coated and novel radial functionally graded dental implants using finite element simulation</t>
@@ -50778,7 +50206,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L752" t="inlineStr"/>
       <c r="M752" t="inlineStr">
         <is>
           <t>SolidWorks;ANSYS</t>
@@ -50791,8 +50218,6 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" t="inlineStr"/>
-      <c r="B753" t="inlineStr"/>
       <c r="C753" t="inlineStr">
         <is>
           <t>Instantaneous and Markerless Registration for Mandible Reconstruction Robot With Fibular Holder</t>
@@ -50836,7 +50261,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L753" t="inlineStr"/>
       <c r="M753" t="inlineStr">
         <is>
           <t>SolidWorks</t>
@@ -50849,8 +50273,6 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" t="inlineStr"/>
-      <c r="B754" t="inlineStr"/>
       <c r="C754" t="inlineStr">
         <is>
           <t>Traditional, 2D and 3D Workflows: What Is Better for Aesthetic Rehabilitation of Superior Anterior Teeth?</t>
@@ -50894,7 +50316,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L754" t="inlineStr"/>
       <c r="M754" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -50907,8 +50328,6 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" t="inlineStr"/>
-      <c r="B755" t="inlineStr"/>
       <c r="C755" t="inlineStr">
         <is>
           <t>Visualizing physiological sclerotic dentin via micro-computed tomography: A pilot study.</t>
@@ -50952,7 +50371,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L755" t="inlineStr"/>
       <c r="M755" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -50965,8 +50383,6 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" t="inlineStr"/>
-      <c r="B756" t="inlineStr"/>
       <c r="C756" t="inlineStr">
         <is>
           <t>An Innovative “Tooth-On-Chip” Microfluidic Device Emulating the Structure and Physiology of the Dental Pulp Tissue</t>
@@ -51010,7 +50426,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L756" t="inlineStr"/>
       <c r="M756" t="inlineStr">
         <is>
           <t>AutoCAD;COMSOL Multiphysics</t>
@@ -51023,8 +50438,6 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" t="inlineStr"/>
-      <c r="B757" t="inlineStr"/>
       <c r="C757" t="inlineStr">
         <is>
           <t>Novel design of additive manufactured hollow porous implants.</t>
@@ -51068,7 +50481,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L757" t="inlineStr"/>
       <c r="M757" t="inlineStr">
         <is>
           <t>ANSYS</t>
@@ -51081,8 +50493,6 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="inlineStr"/>
-      <c r="B758" t="inlineStr"/>
       <c r="C758" t="inlineStr">
         <is>
           <t>Upper Airway Segmentation Based on the Attention Mechanism of Weak Feature Regions</t>
@@ -51126,7 +50536,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L758" t="inlineStr"/>
       <c r="M758" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -51139,8 +50548,6 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" t="inlineStr"/>
-      <c r="B759" t="inlineStr"/>
       <c r="C759" t="inlineStr">
         <is>
           <t>Spontaneous dental implant macro-migration in low-density bone: An 8-year case report.</t>
@@ -51184,7 +50591,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L759" t="inlineStr"/>
       <c r="M759" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -51197,8 +50603,6 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" t="inlineStr"/>
-      <c r="B760" t="inlineStr"/>
       <c r="C760" t="inlineStr">
         <is>
           <t>Effect of platform design of dental implant abutment on loosening and fatigue performance</t>
@@ -51242,7 +50646,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L760" t="inlineStr"/>
       <c r="M760" t="inlineStr">
         <is>
           <t>SolidWorks;ANSYS Workbench</t>
@@ -51255,8 +50658,6 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" t="inlineStr"/>
-      <c r="B761" t="inlineStr"/>
       <c r="C761" t="inlineStr">
         <is>
           <t>Clinical evaluation of a one-piece polyetheretherketone removable partial denture fabricated using a novel digital workflow: A self-controlled clinical trial</t>
@@ -51300,7 +50701,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L761" t="inlineStr"/>
       <c r="M761" t="inlineStr">
         <is>
           <t>Geomagic Studio</t>
@@ -51313,8 +50713,6 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" t="inlineStr"/>
-      <c r="B762" t="inlineStr"/>
       <c r="C762" t="inlineStr">
         <is>
           <t>Effect of preparation design and scan pattern on the accuracy of intraoral scans for complete arch laminate veneers under simulated intraoral variables</t>
@@ -51358,7 +50756,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -51371,8 +50768,6 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" t="inlineStr"/>
-      <c r="B763" t="inlineStr"/>
       <c r="C763" t="inlineStr">
         <is>
           <t>Estimating Reference Shape Model for Personalized Surgical Reconstruction of Craniomaxillofacial Defects</t>
@@ -51416,7 +50811,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L763" t="inlineStr"/>
       <c r="M763" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -51429,8 +50823,6 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="inlineStr"/>
-      <c r="B764" t="inlineStr"/>
       <c r="C764" t="inlineStr">
         <is>
           <t>Fractured Full-Arch Tooth-Supported Zirconia Bridge: Thin Design, Surface Damage, and Excessive Cement Layer Thickness.</t>
@@ -51474,7 +50866,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L764" t="inlineStr"/>
       <c r="M764" t="inlineStr">
         <is>
           <t>Rhinoceros</t>
@@ -51487,8 +50878,6 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="inlineStr"/>
-      <c r="B765" t="inlineStr"/>
       <c r="C765" t="inlineStr">
         <is>
           <t>Influence of Transmucosal Contour on Peri-Implant Soft Tissue Dimensions: A Cross-Sectional Study in Posterior Single-Tooth Implants.</t>
@@ -51532,7 +50921,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L765" t="inlineStr"/>
       <c r="M765" t="inlineStr">
         <is>
           <t>Geomagic Control X;AutoCAD</t>
@@ -51545,8 +50933,6 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" t="inlineStr"/>
-      <c r="B766" t="inlineStr"/>
       <c r="C766" t="inlineStr">
         <is>
           <t>The link between abutment configuration and marginal bone loss in subcrestally placed posterior implant-supported restorations</t>
@@ -51590,7 +50976,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L766" t="inlineStr"/>
       <c r="M766" t="inlineStr">
         <is>
           <t>AutoCAD</t>
@@ -51603,8 +50988,6 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="inlineStr"/>
-      <c r="B767" t="inlineStr"/>
       <c r="C767" t="inlineStr">
         <is>
           <t>Predicting site-specific alveolar bone remodeling in class III decompensation: a preliminary study based on a data-driven RBF framework.</t>
@@ -51648,7 +51031,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L767" t="inlineStr"/>
       <c r="M767" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -51661,8 +51043,6 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" t="inlineStr"/>
-      <c r="B768" t="inlineStr"/>
       <c r="C768" t="inlineStr">
         <is>
           <t>Objective characterization of dental occlusal and fissure morphologies: Method development and exploratory analysis</t>
@@ -51706,7 +51086,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L768" t="inlineStr"/>
       <c r="M768" t="inlineStr">
         <is>
           <t>MeshLab;Geomagic Wrap</t>
@@ -51719,8 +51098,6 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" t="inlineStr"/>
-      <c r="B769" t="inlineStr"/>
       <c r="C769" t="inlineStr">
         <is>
           <t>Effect of peri-implant bone resorption on mechanical stress in the implant body: In vivo measured load-based finite element analysis</t>
@@ -51764,7 +51141,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L769" t="inlineStr"/>
       <c r="M769" t="inlineStr">
         <is>
           <t>SolidWorks</t>
@@ -51777,8 +51153,6 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" t="inlineStr"/>
-      <c r="B770" t="inlineStr"/>
       <c r="C770" t="inlineStr">
         <is>
           <t>Influence of different education approaches on the implantation performance of dental practitioners in aesthetic zone.</t>
@@ -51822,7 +51196,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L770" t="inlineStr"/>
       <c r="M770" t="inlineStr">
         <is>
           <t>Geomagic Studio</t>
@@ -51835,8 +51208,6 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="inlineStr"/>
-      <c r="B771" t="inlineStr"/>
       <c r="C771" t="inlineStr">
         <is>
           <t>Biomechanical effect of implant thickness and screw diameter on CFR-PEEK subperiosteal implants: a three-dimensional finite element analysis</t>
@@ -51880,7 +51251,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L771" t="inlineStr"/>
       <c r="M771" t="inlineStr">
         <is>
           <t>3D Slicer;Blender;HyperMesh</t>
@@ -51893,8 +51263,6 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" t="inlineStr"/>
-      <c r="B772" t="inlineStr"/>
       <c r="C772" t="inlineStr">
         <is>
           <t>A digital workflow for pair matching of maxillary anterior teeth using a 3D segmentation technique for esthetic implant restorations</t>
@@ -51938,7 +51306,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L772" t="inlineStr"/>
       <c r="M772" t="inlineStr">
         <is>
           <t>3D Slicer;MeshLab</t>
@@ -51951,8 +51318,6 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" t="inlineStr"/>
-      <c r="B773" t="inlineStr"/>
       <c r="C773" t="inlineStr">
         <is>
           <t>Dynamic navigation for prosthetically driven zygomatic implant placement in extensive maxillary defects: Results of a prospective case series</t>
@@ -51996,7 +51361,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L773" t="inlineStr"/>
       <c r="M773" t="inlineStr">
         <is>
           <t>Brainlab iPlan</t>
@@ -52009,8 +51373,6 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" t="inlineStr"/>
-      <c r="B774" t="inlineStr"/>
       <c r="C774" t="inlineStr">
         <is>
           <t>Influence of Intraoral Scanners, Operators, and Data Processing on Dimensional Accuracy of Dental Casts for Unsupervised Clinical Machine Learning: An In Vitro  Comparative Study.</t>
@@ -52054,7 +51416,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L774" t="inlineStr"/>
       <c r="M774" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -52067,8 +51428,6 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="inlineStr"/>
-      <c r="B775" t="inlineStr"/>
       <c r="C775" t="inlineStr">
         <is>
           <t>Clinical factors influencing implant positioning by guided surgery using a nonmetal sleeve template in the partially edentulous ridge: Multiple regression analysis of a prospective cohort</t>
@@ -52112,7 +51471,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L775" t="inlineStr"/>
       <c r="M775" t="inlineStr">
         <is>
           <t>Geomagic Verify</t>
@@ -52125,8 +51483,6 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" t="inlineStr"/>
-      <c r="B776" t="inlineStr"/>
       <c r="C776" t="inlineStr">
         <is>
           <t>DentalArch: AI-Based Arch Shape Detection in Orthodontics</t>
@@ -52170,7 +51526,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L776" t="inlineStr"/>
       <c r="M776" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -52183,8 +51538,6 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" t="inlineStr"/>
-      <c r="B777" t="inlineStr"/>
       <c r="C777" t="inlineStr">
         <is>
           <t>Fit and retention of complete denture bases: Part I e Conventional versus CAD-CAM methods: A clinical controlled crossover study</t>
@@ -52228,7 +51581,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L777" t="inlineStr"/>
       <c r="M777" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -52241,8 +51593,6 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" t="inlineStr"/>
-      <c r="B778" t="inlineStr"/>
       <c r="C778" t="inlineStr">
         <is>
           <t>Influence of exposure protocol, voxel size, and artifact removal algorithm on the trueness of segmentation utilizing an artificial-intelligence-based system</t>
@@ -52286,7 +51636,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L778" t="inlineStr"/>
       <c r="M778" t="inlineStr">
         <is>
           <t>Meshmixer;Geomagic Design X</t>
@@ -52299,8 +51648,6 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" t="inlineStr"/>
-      <c r="B779" t="inlineStr"/>
       <c r="C779" t="inlineStr">
         <is>
           <t>Custom design of a temporomandibular joint prosthesis: A kinematic approach evaluated by finite element analysis</t>
@@ -52344,7 +51691,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L779" t="inlineStr"/>
       <c r="M779" t="inlineStr">
         <is>
           <t>Mimics;Rhinoceros;ANSYS</t>
@@ -52357,8 +51703,6 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" t="inlineStr"/>
-      <c r="B780" t="inlineStr"/>
       <c r="C780" t="inlineStr">
         <is>
           <t>Application of temporary patient-specific plate in head and neck osteocutaneous free flap reconstruction: a prospective pilot study.</t>
@@ -52402,7 +51746,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L780" t="inlineStr"/>
       <c r="M780" t="inlineStr">
         <is>
           <t>3-Matic</t>
@@ -52415,8 +51758,6 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" t="inlineStr"/>
-      <c r="B781" t="inlineStr"/>
       <c r="C781" t="inlineStr">
         <is>
           <t>Electromagnetic Navigation in Mandibular Reconstruction Using Autologous Grafts: A Color-Coded Assistance for Precise Positioning of Bone Segments.</t>
@@ -52460,7 +51801,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L781" t="inlineStr"/>
       <c r="M781" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -52473,8 +51813,6 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" t="inlineStr"/>
-      <c r="B782" t="inlineStr"/>
       <c r="C782" t="inlineStr">
         <is>
           <t>Optimization of Resin Printing Parameters for Improved Surface Roughness Using Metaheuristic Algorithms: A Multifaceted Approach</t>
@@ -52518,7 +51856,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L782" t="inlineStr"/>
       <c r="M782" t="inlineStr">
         <is>
           <t>Fusion 360</t>
@@ -52531,8 +51868,6 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="inlineStr"/>
-      <c r="B783" t="inlineStr"/>
       <c r="C783" t="inlineStr">
         <is>
           <t>Experimental study on dimensional variations of 3D printed dental models based on printing orientation.</t>
@@ -52576,7 +51911,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L783" t="inlineStr"/>
       <c r="M783" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -52589,8 +51923,6 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" t="inlineStr"/>
-      <c r="B784" t="inlineStr"/>
       <c r="C784" t="inlineStr">
         <is>
           <t>Automated micro-CT quantification of clear aligner fit: a pilot comparison of manufacturing processes.</t>
@@ -52634,7 +51966,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L784" t="inlineStr"/>
       <c r="M784" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -52647,8 +51978,6 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" t="inlineStr"/>
-      <c r="B785" t="inlineStr"/>
       <c r="C785" t="inlineStr">
         <is>
           <t>A Smart Projective Imaging and Navigation System for Oral and Maxillofacial Surgery</t>
@@ -52692,7 +52021,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L785" t="inlineStr"/>
       <c r="M785" t="inlineStr">
         <is>
           <t>Blender</t>
@@ -52705,8 +52033,6 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" t="inlineStr"/>
-      <c r="B786" t="inlineStr"/>
       <c r="C786" t="inlineStr">
         <is>
           <t>Zirconia endocrown with intracanal extension and zi posts on maxillary molars: in silico study</t>
@@ -52750,7 +52076,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L786" t="inlineStr"/>
       <c r="M786" t="inlineStr">
         <is>
           <t>Rhinoceros;VRMesh;ALGOR</t>
@@ -52763,8 +52088,6 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" t="inlineStr"/>
-      <c r="B787" t="inlineStr"/>
       <c r="C787" t="inlineStr">
         <is>
           <t>Evaluation of the Retentive Forces from Removable Partial Denture Clasps Manufactured by the Digital Method</t>
@@ -52808,7 +52131,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L787" t="inlineStr"/>
       <c r="M787" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -52821,8 +52143,6 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" t="inlineStr"/>
-      <c r="B788" t="inlineStr"/>
       <c r="C788" t="inlineStr">
         <is>
           <t>Fully automated 3D segmentation of periapical lesions on CBCT images using nnU-Net v2</t>
@@ -52866,7 +52186,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L788" t="inlineStr"/>
       <c r="M788" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -52879,8 +52198,6 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" t="inlineStr"/>
-      <c r="B789" t="inlineStr"/>
       <c r="C789" t="inlineStr">
         <is>
           <t>Age-related changes in the parotid gland: a computed tomography-based radiomics study.</t>
@@ -52924,7 +52241,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L789" t="inlineStr"/>
       <c r="M789" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -52937,8 +52253,6 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" t="inlineStr"/>
-      <c r="B790" t="inlineStr"/>
       <c r="C790" t="inlineStr">
         <is>
           <t>Direction-oriented fiber guiding with a tunable tri-layer-3D scaffold for periodontal regeneration</t>
@@ -52982,7 +52296,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L790" t="inlineStr"/>
       <c r="M790" t="inlineStr">
         <is>
           <t>VGStudio MAX;Creo</t>
@@ -52995,8 +52308,6 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="inlineStr"/>
-      <c r="B791" t="inlineStr"/>
       <c r="C791" t="inlineStr">
         <is>
           <t>Tissue surface adaptation and retention of digital obturator after one year of use</t>
@@ -53040,7 +52351,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L791" t="inlineStr"/>
       <c r="M791" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -53053,8 +52363,6 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" t="inlineStr"/>
-      <c r="B792" t="inlineStr"/>
       <c r="C792" t="inlineStr">
         <is>
           <t>Biomechanical Effects of Platform Diameter and Screw Length in an Abutment-Free Tissue-Level Implant System Compared with a Ti-Base Configuration: 3D Finite Element Analysis</t>
@@ -53098,7 +52406,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L792" t="inlineStr"/>
       <c r="M792" t="inlineStr">
         <is>
           <t>ANSYS Workbench;ANSYS Mechanical;SpaceClaim;ANSYS DesignModeler</t>
@@ -53111,8 +52418,6 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="inlineStr"/>
-      <c r="B793" t="inlineStr"/>
       <c r="C793" t="inlineStr">
         <is>
           <t>Does the fixture thread depth affect the accuracy of implant placement during fully guided immediate implant placement?: A human cadaver study.</t>
@@ -53156,7 +52461,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L793" t="inlineStr"/>
       <c r="M793" t="inlineStr">
         <is>
           <t>Geomagic Verify</t>
@@ -53169,8 +52473,6 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" t="inlineStr"/>
-      <c r="B794" t="inlineStr"/>
       <c r="C794" t="inlineStr">
         <is>
           <t>Root canal treatment planning by automatic tooth and root canal segmentation in dental CBCT with deep multi-task feature learning</t>
@@ -53214,7 +52516,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L794" t="inlineStr"/>
       <c r="M794" t="inlineStr">
         <is>
           <t>ITK-SNAP</t>
@@ -53227,8 +52528,6 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" t="inlineStr"/>
-      <c r="B795" t="inlineStr"/>
       <c r="C795" t="inlineStr">
         <is>
           <t>A New Method to Evaluate Trueness and Precision of Digital and Conventional Impression Techniques for Complete Dental Arch</t>
@@ -53272,7 +52571,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L795" t="inlineStr"/>
       <c r="M795" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -53285,8 +52583,6 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" t="inlineStr"/>
-      <c r="B796" t="inlineStr"/>
       <c r="C796" t="inlineStr">
         <is>
           <t>Development of Micro-CT-Based Anatomically Accurate Tooth Model for Finite Element Analysis of Composite Restorations.</t>
@@ -53330,7 +52626,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L796" t="inlineStr"/>
       <c r="M796" t="inlineStr">
         <is>
           <t>3D Slicer;Solid Edge;Blender</t>
@@ -53343,8 +52638,6 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" t="inlineStr"/>
-      <c r="B797" t="inlineStr"/>
       <c r="C797" t="inlineStr">
         <is>
           <t>Digital duplication of maxillary complete denture: A dental technique.</t>
@@ -53388,7 +52681,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L797" t="inlineStr"/>
       <c r="M797" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -53401,8 +52693,6 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="inlineStr"/>
-      <c r="B798" t="inlineStr"/>
       <c r="C798" t="inlineStr">
         <is>
           <t>Rehabilitation of the Severely Atrophic Maxilla with Subperiosteal Implants: A Biomechanical and Decision Analysis of Material and Configuration Choices.</t>
@@ -53446,7 +52736,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L798" t="inlineStr"/>
       <c r="M798" t="inlineStr">
         <is>
           <t>SolidWorks;ABAQUS</t>
@@ -53459,8 +52748,6 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="inlineStr"/>
-      <c r="B799" t="inlineStr"/>
       <c r="C799" t="inlineStr">
         <is>
           <t>Three-dimensional finite element analysis of temporomandibular joint stresses following botulinum toxin injection and occlusal splint therapy in bruxism.</t>
@@ -53504,7 +52791,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L799" t="inlineStr"/>
       <c r="M799" t="inlineStr">
         <is>
           <t>3D Slicer;SpaceClaim;ANSYS Workbench;LS-DYNA</t>
@@ -53517,8 +52803,6 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="inlineStr"/>
-      <c r="B800" t="inlineStr"/>
       <c r="C800" t="inlineStr">
         <is>
           <t>An open-source AI tool for predicting cephalometric measurements from clinical data and photographic images</t>
@@ -53562,7 +52846,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L800" t="inlineStr"/>
       <c r="M800" t="inlineStr">
         <is>
           <t>Meshmixer</t>
@@ -53575,8 +52858,6 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="inlineStr"/>
-      <c r="B801" t="inlineStr"/>
       <c r="C801" t="inlineStr">
         <is>
           <t>Automatic three-dimensional facial symmetry reference plane construction based on facial planar reflective symmetry net</t>
@@ -53620,7 +52901,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L801" t="inlineStr"/>
       <c r="M801" t="inlineStr">
         <is>
           <t>Geomagic Wrap</t>
@@ -53633,8 +52913,6 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="inlineStr"/>
-      <c r="B802" t="inlineStr"/>
       <c r="C802" t="inlineStr">
         <is>
           <t>In vivo trueness of full-arch implant-supported CAD/CAM restorations and models based on conventional impressions</t>
@@ -53678,7 +52956,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L802" t="inlineStr"/>
       <c r="M802" t="inlineStr">
         <is>
           <t>Geomagic Design X;Geomagic Control X</t>
@@ -53691,8 +52968,6 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="inlineStr"/>
-      <c r="B803" t="inlineStr"/>
       <c r="C803" t="inlineStr">
         <is>
           <t>Quantitative and qualitative evaluation of precision in dental 3D facial scanning across handheld, fixed multicamera, and smartphone depth-sensing systems.</t>
@@ -53736,7 +53011,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L803" t="inlineStr"/>
       <c r="M803" t="inlineStr">
         <is>
           <t>Geomagic Control X;Meshmixer</t>
@@ -53749,8 +53023,6 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="inlineStr"/>
-      <c r="B804" t="inlineStr"/>
       <c r="C804" t="inlineStr">
         <is>
           <t>Three-dimensional finite element analysis of zygomatic and pterygoid implants for the rehabilitation of severely atrophic maxilla</t>
@@ -53794,7 +53066,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L804" t="inlineStr"/>
       <c r="M804" t="inlineStr">
         <is>
           <t>Mimics;Geomagic Design X;SolidWorks</t>
@@ -53807,8 +53078,6 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="inlineStr"/>
-      <c r="B805" t="inlineStr"/>
       <c r="C805" t="inlineStr">
         <is>
           <t>A novel method of 3D printing locating guide for abutment screw removal in cement- retained implant-supported prostheses</t>
@@ -53852,7 +53121,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L805" t="inlineStr"/>
       <c r="M805" t="inlineStr">
         <is>
           <t>Magics</t>
@@ -53865,8 +53133,6 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="inlineStr"/>
-      <c r="B806" t="inlineStr"/>
       <c r="C806" t="inlineStr">
         <is>
           <t>Trueness of the apical and middle root portion segments of 3D-printed removable die and alveolar cast designs manufactured using stereolithographic 3D printing</t>
@@ -53910,7 +53176,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L806" t="inlineStr"/>
       <c r="M806" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -53923,8 +53188,6 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="inlineStr"/>
-      <c r="B807" t="inlineStr"/>
       <c r="C807" t="inlineStr">
         <is>
           <t>Noncarious cervical lesions in the aging population analyzed through digital scanning: occlusal risk factors, dimensions, and morphology</t>
@@ -53968,7 +53231,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L807" t="inlineStr"/>
       <c r="M807" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -53981,8 +53243,6 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="inlineStr"/>
-      <c r="B808" t="inlineStr"/>
       <c r="C808" t="inlineStr">
         <is>
           <t>Efficacy of Submucosal Polydeoxyribonucleotide Injection after Impacted Mandibular Third Molar Extraction: A Randomized Controlled Trial</t>
@@ -54026,7 +53286,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L808" t="inlineStr"/>
       <c r="M808" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -54039,8 +53298,6 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="inlineStr"/>
-      <c r="B809" t="inlineStr"/>
       <c r="C809" t="inlineStr">
         <is>
           <t>Early-stage stability and degradation of patient-specific biodegradable 3D-printed implants for critical mandibular reconstruction</t>
@@ -54084,7 +53341,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L809" t="inlineStr"/>
       <c r="M809" t="inlineStr">
         <is>
           <t>ANSYS Workbench</t>
@@ -54097,8 +53353,6 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="inlineStr"/>
-      <c r="B810" t="inlineStr"/>
       <c r="C810" t="inlineStr">
         <is>
           <t>Vertical and Horizontal Ridge Augmentation Using Customized Three-Dimensionally Printed Polycaprolactone Mesh in Atrophic Posterior Maxillae: A Case Report</t>
@@ -54142,7 +53396,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L810" t="inlineStr"/>
       <c r="M810" t="inlineStr">
         <is>
           <t>PowerShape</t>
@@ -54155,8 +53408,6 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="inlineStr"/>
-      <c r="B811" t="inlineStr"/>
       <c r="C811" t="inlineStr">
         <is>
           <t>Biomechanical Analysis of Different Pacifiers and Their Effects on the Upper Jaw and Tongue</t>
@@ -54200,7 +53451,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L811" t="inlineStr"/>
       <c r="M811" t="inlineStr">
         <is>
           <t>SolidWorks</t>
@@ -54213,8 +53463,6 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="inlineStr"/>
-      <c r="B812" t="inlineStr"/>
       <c r="C812" t="inlineStr">
         <is>
           <t>Augmented Reality-Assisted Surgical Exposure of an Impacted Tooth: A Pilot Study</t>
@@ -54258,7 +53506,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L812" t="inlineStr"/>
       <c r="M812" t="inlineStr">
         <is>
           <t>Meshmixer;InVesalius</t>
@@ -54271,8 +53518,6 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="inlineStr"/>
-      <c r="B813" t="inlineStr"/>
       <c r="C813" t="inlineStr">
         <is>
           <t>Concurrent computed tomography-based evaluation of nasal morphology, airway volume, and skeletal changes following craniofacial distraction osteogenesis: A  pilot retrospective case series.</t>
@@ -54316,7 +53561,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L813" t="inlineStr"/>
       <c r="M813" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -54329,8 +53573,6 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="inlineStr"/>
-      <c r="B814" t="inlineStr"/>
       <c r="C814" t="inlineStr">
         <is>
           <t>Accuracy of intraoral optical scan versus stereophotogrammetry for complete-arch digital implant impression: An in vitro study.</t>
@@ -54374,7 +53616,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L814" t="inlineStr"/>
       <c r="M814" t="inlineStr">
         <is>
           <t>Geomagic Studio;hyperCAD-S</t>
@@ -54387,8 +53628,6 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="inlineStr"/>
-      <c r="B815" t="inlineStr"/>
       <c r="C815" t="inlineStr">
         <is>
           <t>A platform combining automatic segmentation and automatic measurement of the maxillary sinus and adjacent structures</t>
@@ -54432,7 +53671,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L815" t="inlineStr"/>
       <c r="M815" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -54445,8 +53683,6 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="inlineStr"/>
-      <c r="B816" t="inlineStr"/>
       <c r="C816" t="inlineStr">
         <is>
           <t>Differentiation of benign and malignant oral lesions through surface texture analysis and SVM modeling</t>
@@ -54490,7 +53726,6 @@
           <t>Morphological and Phenotypic Analysis</t>
         </is>
       </c>
-      <c r="L816" t="inlineStr"/>
       <c r="M816" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -54503,8 +53738,6 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="inlineStr"/>
-      <c r="B817" t="inlineStr"/>
       <c r="C817" t="inlineStr">
         <is>
           <t>Investigation of Conventional vs Nonoriginal CAD/CAM Bars with Production Stage Differences: An In Vitro Precision Study Using a Novel Technique</t>
@@ -54548,7 +53781,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L817" t="inlineStr"/>
       <c r="M817" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -54561,8 +53793,6 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="inlineStr"/>
-      <c r="B818" t="inlineStr"/>
       <c r="C818" t="inlineStr">
         <is>
           <t>A TMPS-designed personalized mandibular scaffolds with optimized SLA parameters and mechanical properties</t>
@@ -54606,7 +53836,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L818" t="inlineStr"/>
       <c r="M818" t="inlineStr">
         <is>
           <t>Mimics;Magics</t>
@@ -54619,8 +53848,6 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="inlineStr"/>
-      <c r="B819" t="inlineStr"/>
       <c r="C819" t="inlineStr">
         <is>
           <t>Bone-Implant Osseointegration Monitoring Using Electro-mechanical Impedance Technique and Convolutional Neural Network: A Numerical Study</t>
@@ -54664,7 +53891,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L819" t="inlineStr"/>
       <c r="M819" t="inlineStr">
         <is>
           <t>COMSOL Multiphysics</t>
@@ -54677,8 +53903,6 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" t="inlineStr"/>
-      <c r="B820" t="inlineStr"/>
       <c r="C820" t="inlineStr">
         <is>
           <t>3D Single-Tooth Reconstruction via Curriculum Learning and Topology-aware Generation</t>
@@ -54722,7 +53946,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L820" t="inlineStr"/>
       <c r="M820" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -54735,8 +53958,6 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" t="inlineStr"/>
-      <c r="B821" t="inlineStr"/>
       <c r="C821" t="inlineStr">
         <is>
           <t>Three-Dimensional Hard and Soft Tissue Healing at Implants With A Modified Neck Design: An In Vivo Preclinical Study</t>
@@ -54780,7 +54001,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L821" t="inlineStr"/>
       <c r="M821" t="inlineStr">
         <is>
           <t>GOM Inspect</t>
@@ -54793,8 +54013,6 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="inlineStr"/>
-      <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr">
         <is>
           <t>Effect of Crestal Position on Bone-Implant Stress Interface of Three-Implant Splinted Prostheses: A Finite Element Analysis</t>
@@ -54838,7 +54056,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L822" t="inlineStr"/>
       <c r="M822" t="inlineStr">
         <is>
           <t>Inventor;ANSYS Workbench</t>
@@ -54851,8 +54068,6 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="inlineStr"/>
-      <c r="B823" t="inlineStr"/>
       <c r="C823" t="inlineStr">
         <is>
           <t>Evaluation of the Effects of Diameter, Length, Splinted or Nonsplinted Form, and Crown-to-Implant Ratio on the Stress Distribution Around Extra-Short Implants in  the Posterior Mandible: Finite Element Analysis.</t>
@@ -54896,7 +54111,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L823" t="inlineStr"/>
       <c r="M823" t="inlineStr">
         <is>
           <t>Mimics;3-Matic;Geomagic Studio;SolidWorks;ANSYS</t>
@@ -54909,8 +54123,6 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="inlineStr"/>
-      <c r="B824" t="inlineStr"/>
       <c r="C824" t="inlineStr">
         <is>
           <t>A reproducible optical-microscopic framework for evaluating electronic apex locator performance in different irrigants using 3D-printed transparent resin  teeth.</t>
@@ -54954,7 +54166,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L824" t="inlineStr"/>
       <c r="M824" t="inlineStr">
         <is>
           <t>3D Slicer;Meshmixer</t>
@@ -54967,8 +54178,6 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="inlineStr"/>
-      <c r="B825" t="inlineStr"/>
       <c r="C825" t="inlineStr">
         <is>
           <t>Effect of various printing parameters on the accuracy (trueness and precision) of 3D-printed partial denture framework</t>
@@ -55012,7 +54221,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L825" t="inlineStr"/>
       <c r="M825" t="inlineStr">
         <is>
           <t>Meshmixer;Geomagic Control X</t>
@@ -55025,8 +54233,6 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="inlineStr"/>
-      <c r="B826" t="inlineStr"/>
       <c r="C826" t="inlineStr">
         <is>
           <t>Accuracy of the Implant Replica Positions on the Complete Edentulous Additive Manufactured Cast.</t>
@@ -55070,7 +54276,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L826" t="inlineStr"/>
       <c r="M826" t="inlineStr">
         <is>
           <t>Geomagic (unspecified)</t>
@@ -55083,8 +54288,6 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="inlineStr"/>
-      <c r="B827" t="inlineStr"/>
       <c r="C827" t="inlineStr">
         <is>
           <t>Influence of planning software and template design on the accuracy of static computer assisted implant surgery performed using guides fabricated with material extrusion technology: An in vitro study</t>
@@ -55128,7 +54331,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L827" t="inlineStr"/>
       <c r="M827" t="inlineStr">
         <is>
           <t>Meshmixer;Geomagic Control X</t>
@@ -55141,8 +54343,6 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="inlineStr"/>
-      <c r="B828" t="inlineStr"/>
       <c r="C828" t="inlineStr">
         <is>
           <t>New Approach to Dental Morphometric Research Based on 3D Imaging Techniques.</t>
@@ -55186,7 +54386,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L828" t="inlineStr"/>
       <c r="M828" t="inlineStr">
         <is>
           <t>Avizo</t>
@@ -55199,8 +54398,6 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="inlineStr"/>
-      <c r="B829" t="inlineStr"/>
       <c r="C829" t="inlineStr">
         <is>
           <t>Tablet-based Augmented reality and 3D printed templates in fully guided Microtia Reconstruction: a clinical workflow.</t>
@@ -55244,7 +54441,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L829" t="inlineStr"/>
       <c r="M829" t="inlineStr">
         <is>
           <t>3D Slicer;Geomagic Freeform</t>
@@ -55257,8 +54453,6 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" t="inlineStr"/>
-      <c r="B830" t="inlineStr"/>
       <c r="C830" t="inlineStr">
         <is>
           <t>Fit and retention of complete denture bases: Part II - conventional impressions versus digital scans: A clinical controlled crossover study.</t>
@@ -55302,7 +54496,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L830" t="inlineStr"/>
       <c r="M830" t="inlineStr">
         <is>
           <t>Geomagic Control X</t>
@@ -55315,8 +54508,6 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" t="inlineStr"/>
-      <c r="B831" t="inlineStr"/>
       <c r="C831" t="inlineStr">
         <is>
           <t>CT-based three-dimensional morphometric analysis of the bony palate and hard palatal mucosa in female orthognathic surgery candidates.</t>
@@ -55360,7 +54551,6 @@
           <t>Morphological and Phenotypic Analysis</t>
         </is>
       </c>
-      <c r="L831" t="inlineStr"/>
       <c r="M831" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -55373,8 +54563,6 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" t="inlineStr"/>
-      <c r="B832" t="inlineStr"/>
       <c r="C832" t="inlineStr">
         <is>
           <t>A high-throughput framework for predicting three-dimensional structural-mechanical relationships of human cranial bones using a deep learning-based method</t>
@@ -55418,7 +54606,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L832" t="inlineStr"/>
       <c r="M832" t="inlineStr">
         <is>
           <t>ABAQUS</t>
@@ -55431,8 +54618,6 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" t="inlineStr"/>
-      <c r="B833" t="inlineStr"/>
       <c r="C833" t="inlineStr">
         <is>
           <t>Toothnroll: An R Package for Landmarking, Measuring, and Mapping Dental Tissues of Hominoid Anterior Teeth</t>
@@ -55476,7 +54661,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L833" t="inlineStr"/>
       <c r="M833" t="inlineStr">
         <is>
           <t>Avizo</t>
@@ -55489,8 +54673,6 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" t="inlineStr"/>
-      <c r="B834" t="inlineStr"/>
       <c r="C834" t="inlineStr">
         <is>
           <t>Three-dimensional evaluation of the effects of Bionator and Forsus appliances on oropharyngeal airway volume in patients with mandibular retrognathia</t>
@@ -55534,7 +54716,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L834" t="inlineStr"/>
       <c r="M834" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -55547,8 +54728,6 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" t="inlineStr"/>
-      <c r="B835" t="inlineStr"/>
       <c r="C835" t="inlineStr">
         <is>
           <t>Clinical validation of the virtual splint registration workflow for craniomaxillofacial surgery</t>
@@ -55592,7 +54771,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L835" t="inlineStr"/>
       <c r="M835" t="inlineStr">
         <is>
           <t>Blender;Brainlab Elements</t>
@@ -55605,8 +54783,6 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" t="inlineStr"/>
-      <c r="B836" t="inlineStr"/>
       <c r="C836" t="inlineStr">
         <is>
           <t>Advances in the Resection and Reconstruction of Midfacial Tumors Through Computer Assisted Surgery</t>
@@ -55650,7 +54826,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L836" t="inlineStr"/>
       <c r="M836" t="inlineStr">
         <is>
           <t>Brainlab iPlan</t>
@@ -55663,8 +54838,6 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" t="inlineStr"/>
-      <c r="B837" t="inlineStr"/>
       <c r="C837" t="inlineStr">
         <is>
           <t>Mineralized osteoblast-derived exosomes and 3D-printed ceramic-based scaffolds for enhanced bone healing: A preclinical exploration</t>
@@ -55708,7 +54881,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L837" t="inlineStr"/>
       <c r="M837" t="inlineStr">
         <is>
           <t>nTop</t>
@@ -55721,8 +54893,6 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" t="inlineStr"/>
-      <c r="B838" t="inlineStr"/>
       <c r="C838" t="inlineStr">
         <is>
           <t>A personalized automated system of 3D facial soft tissue landmarks annotation based on deep learning and computer vision</t>
@@ -55766,7 +54936,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L838" t="inlineStr"/>
       <c r="M838" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -55779,8 +54948,6 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" t="inlineStr"/>
-      <c r="B839" t="inlineStr"/>
       <c r="C839" t="inlineStr">
         <is>
           <t>A 3D Co-Culture System Inspired by Fracture Healing Cell Interactions for Bone Tissue Engineering</t>
@@ -55824,7 +54991,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L839" t="inlineStr"/>
       <c r="M839" t="inlineStr">
         <is>
           <t>Magics</t>
@@ -55837,8 +55003,6 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" t="inlineStr"/>
-      <c r="B840" t="inlineStr"/>
       <c r="C840" t="inlineStr">
         <is>
           <t>Novel standardized method for inducing medication-related osteonecrosis of the jaw in rats and precise quantitative assessment of pathological outcomes</t>
@@ -55882,7 +55046,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L840" t="inlineStr"/>
       <c r="M840" t="inlineStr">
         <is>
           <t>TRI/3D-BON</t>
@@ -55895,8 +55058,6 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="inlineStr"/>
-      <c r="B841" t="inlineStr"/>
       <c r="C841" t="inlineStr">
         <is>
           <t>Osteogenic Potential of 3D-Printed Porous Poly(lactide-co-trimethylene carbonate) Scaffolds Coated with Mg-Doped Hydroxyapatite</t>
@@ -55940,7 +55101,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L841" t="inlineStr"/>
       <c r="M841" t="inlineStr">
         <is>
           <t>COMSOL Multiphysics</t>
@@ -55953,8 +55113,6 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="inlineStr"/>
-      <c r="B842" t="inlineStr"/>
       <c r="C842" t="inlineStr">
         <is>
           <t>Mixed Reality as a Digital Visualisation Solution for the Head and Neck Tumour Board: Application Creation and Implementation Study</t>
@@ -55998,7 +55156,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L842" t="inlineStr"/>
       <c r="M842" t="inlineStr">
         <is>
           <t>Brainlab Elements;Brainlab Mixed Reality Viewer</t>
@@ -56011,8 +55168,6 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="inlineStr"/>
-      <c r="B843" t="inlineStr"/>
       <c r="C843" t="inlineStr">
         <is>
           <t>Morphology and Function Dual-Adjustable Biomimetic 4D-Printed Scaffold for the Regenerative Restoration of Complex Bone Defects</t>
@@ -56056,7 +55211,6 @@
           <t>Digital Design and Manufacturing</t>
         </is>
       </c>
-      <c r="L843" t="inlineStr"/>
       <c r="M843" t="inlineStr">
         <is>
           <t>Creo</t>
@@ -56069,8 +55223,6 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="inlineStr"/>
-      <c r="B844" t="inlineStr"/>
       <c r="C844" t="inlineStr">
         <is>
           <t>Refined Surgical Protocol for the Insertion of Bioactive-coated Titanium Microscrews in the Rat Tibia</t>
@@ -56114,7 +55266,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L844" t="inlineStr"/>
       <c r="M844" t="inlineStr">
         <is>
           <t>Dragonfly</t>
@@ -56127,8 +55278,6 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="inlineStr"/>
-      <c r="B845" t="inlineStr"/>
       <c r="C845" t="inlineStr">
         <is>
           <t>Multiclass CBCT Image Segmentation for Orthodontics with Deep Learning</t>
@@ -56172,7 +55321,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L845" t="inlineStr"/>
       <c r="M845" t="inlineStr">
         <is>
           <t>Mimics</t>
@@ -56185,8 +55333,6 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" t="inlineStr"/>
-      <c r="B846" t="inlineStr"/>
       <c r="C846" t="inlineStr">
         <is>
           <t>Mixed reality combined with surgical navigation versus conventional navigation for resection of oral and maxillofacial tumors: a comparative study</t>
@@ -56230,7 +55376,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L846" t="inlineStr"/>
       <c r="M846" t="inlineStr">
         <is>
           <t>Brainlab iPlan;Geomagic Control X</t>
@@ -56243,8 +55388,6 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" t="inlineStr"/>
-      <c r="B847" t="inlineStr"/>
       <c r="C847" t="inlineStr">
         <is>
           <t>Optimization of PETG 3D printing parameters for the design and development of biocompatible bone implants</t>
@@ -56288,7 +55431,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L847" t="inlineStr"/>
       <c r="M847" t="inlineStr">
         <is>
           <t>3D Slicer</t>
@@ -56301,8 +55443,6 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" t="inlineStr"/>
-      <c r="B848" t="inlineStr"/>
       <c r="C848" t="inlineStr">
         <is>
           <t>Increased rate of pseudarthrosis in the anterior intersegmental gap after mandibular reconstruction with fibula free flaps: a volumetric analysis</t>
@@ -56346,7 +55486,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L848" t="inlineStr"/>
       <c r="M848" t="inlineStr">
         <is>
           <t>ImageJ</t>
@@ -56359,8 +55498,6 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" t="inlineStr"/>
-      <c r="B849" t="inlineStr"/>
       <c r="C849" t="inlineStr">
         <is>
           <t>Principal component analysis of 3-dimensional facial soft-tissue morphology in three adult populations</t>
@@ -56404,7 +55541,6 @@
           <t>Morphological and Phenotypic Analysis</t>
         </is>
       </c>
-      <c r="L849" t="inlineStr"/>
       <c r="M849" t="inlineStr">
         <is>
           <t>RadiAnt DICOM Viewer</t>
@@ -56417,8 +55553,6 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" t="inlineStr"/>
-      <c r="B850" t="inlineStr"/>
       <c r="C850" t="inlineStr">
         <is>
           <t>Enhancing Maxillofacial Surgery: 3D-Printed Models from CT Scans for Improved Surgical Planning</t>
@@ -56462,7 +55596,6 @@
           <t>Surgical Planning and Precise Implementation</t>
         </is>
       </c>
-      <c r="L850" t="inlineStr"/>
       <c r="M850" t="inlineStr">
         <is>
           <t>Mimics;3-Matic</t>
@@ -56475,8 +55608,6 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="inlineStr"/>
-      <c r="B851" t="inlineStr"/>
       <c r="C851" t="inlineStr">
         <is>
           <t>Tooth Segmentation of Dental Mesh Based on Improved Region Growing</t>
@@ -56520,7 +55651,6 @@
           <t>Image Segmentation and 3D Reconstruction</t>
         </is>
       </c>
-      <c r="L851" t="inlineStr"/>
       <c r="M851" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -56533,8 +55663,6 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" t="inlineStr"/>
-      <c r="B852" t="inlineStr"/>
       <c r="C852" t="inlineStr">
         <is>
           <t>Face analyzer 3D: Automatic facial profile detection and occlusion classification for dental purposes</t>
@@ -56578,7 +55706,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L852" t="inlineStr"/>
       <c r="M852" t="inlineStr">
         <is>
           <t>MeshLab</t>
@@ -56591,8 +55718,6 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="inlineStr"/>
-      <c r="B853" t="inlineStr"/>
       <c r="C853" t="inlineStr">
         <is>
           <t>Effect of bar material on the biomechanical performance of hybrid dental prosthesis</t>
@@ -56636,7 +55761,6 @@
           <t>Biomechanical Analysis and Simulation</t>
         </is>
       </c>
-      <c r="L853" t="inlineStr"/>
       <c r="M853" t="inlineStr">
         <is>
           <t>ANSYS;SolidWorks</t>
@@ -56649,8 +55773,6 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="inlineStr"/>
-      <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
           <t>Type of maxillary segment mobilization affects three-dimensional nasal morphology</t>
@@ -56694,7 +55816,6 @@
           <t>3D Data Analysis and Accuracy Assessment</t>
         </is>
       </c>
-      <c r="L854" t="inlineStr"/>
       <c r="M854" t="inlineStr">
         <is>
           <t>Geomagic (unspecified)</t>
@@ -60417,21 +59538,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>序号</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -60449,14 +59571,24 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>裁定理由</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>审核轮次</t>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Reason for verdict</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Reason for verdict (original Chinese)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Review round</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Review round (original Chinese)</t>
         </is>
       </c>
     </row>
@@ -60474,13 +59606,22 @@
           <t>journalArticle</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>PDF verified: only dental-specific software (Navident / EvaluNav)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>PDF verified: only dental-specific software (Navident / EvaluNav)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PDF verification</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>PDF 核验</t>
         </is>
@@ -60500,13 +59641,22 @@
           <t>journalArticle</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>PDF verified: only dental-specific software (NEMOfab / Nemotec)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>PDF verified: only dental-specific software (NEMOfab / Nemotec)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>PDF verification</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>PDF 核验</t>
         </is>
@@ -60526,13 +59676,22 @@
           <t>journalArticle</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>No full text available; software (Robins 3D) could not be verified</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>No full text available; software (Robins 3D) could not be verified</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>PDF verification</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>PDF 核验</t>
         </is>
@@ -60559,10 +59718,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Outside the search time window (2026-08; the prespecified inclusion window was 2020-07-01 to 2026-06-30); excluded strictly according to the prespecified time window</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>检索时间窗之外（2026-08；预设纳入窗为 2020-07-01 至 2026-06-30），严格按预设时间窗剔除</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Time window verification</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>时间窗核验</t>
         </is>
@@ -60589,10 +59758,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Outside the search time window (2026-08; the prespecified inclusion window was 2020-07-01 to 2026-06-30); excluded strictly according to the prespecified time window</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>检索时间窗之外（2026-08；预设纳入窗为 2020-07-01 至 2026-06-30），严格按预设时间窗剔除</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Time window verification</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>时间窗核验</t>
         </is>
@@ -60619,10 +59798,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Outside the search time window (2020-05; the prespecified inclusion window was 2020-07-01 to 2026-06-30); excluded strictly according to the prespecified time window</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>检索时间窗之外（2020-05；预设纳入窗为 2020-07-01 至 2026-06-30），严格按预设时间窗剔除</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Time window verification</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>时间窗核验</t>
         </is>
@@ -60649,10 +59838,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): the title explicitly labels it as a "narrative review", which belongs to the review literature category and does not meet the criteria for original research, technical notes, or case reports</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：标题明确标注为"narrative review"，属于综述类文献，不符合原创研究、技术说明或病例报</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60679,10 +59878,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Borderline case, determined upon assessment to fall outside the oral cavity scope (neither the journal nor the abstract pertains to oral medicine): this article is an engineering control study of a chewing robot, belonging to the robotics/engineering field, and</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>边界情形，经研判属非口腔范畴（期刊与摘要均非口腔医学）：该文献为咀嚼机器人（chewing robot）的工程控制研究，属于机器人/工程领域，并</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60709,10 +59918,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Conference paper and non-dental/demonstration type</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>会议论文且为非牙科/演示类</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60739,10 +59958,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Conference paper and non-dental/demonstration type</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>会议论文且为非牙科/演示类</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60769,10 +59998,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Outside the scope of oral medicine: this article studies a simulated surgical training platform for percutaneous nephrolithotomy (PCNL), which belongs to the field of urology/nephrology and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献研究的是经皮肾镜取石术（PCNL）的模拟手术演练平台，属于泌尿外科/肾脏领域，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60799,10 +60038,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): the title explicitly labels it as a "systematic review", which is a non-original research type and does not meet the inclusion criteria</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：标题明确标注为"systematic review"（系统综述），属于非原创研究类型，不符合纳入标准</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60829,10 +60078,20 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The title explicitly labels it as a "Scoping Review," and the abstract also states that it is a scoping review conducted according to PRISMA guidelines, belonging to</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：标题明确标注为"Scoping Review"，摘要也说明是按照PRISMA指南进行的范围综述，属于</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60859,10 +60118,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>Borderline case, judged to be outside the oral medicine scope (neither the journal nor the abstract is in oral medicine): This study is on 3D-printed scaffold materials in the field of bone tissue engineering (not oral medicine), and is unrelated to clinical practice or research in oral medicine</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>边界情形，经研判属非口腔范畴（期刊与摘要均非口腔医学）：该研究为骨组织工程（非口腔医学）领域的3D打印支架材料研究，与口腔医学临床实践或研究无关</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60889,10 +60158,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article studies the quality of 3D ultrasound imaging for resection margin assessment in tumor surgery, belonging to the field of oncologic surgery/imaging engineering, and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献研究的是肿瘤手术中切除边缘评估的3D超声成像质量，属于肿瘤外科/影像工程领域，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60919,10 +60198,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Borderline case, judged to be outside the oral medicine scope (neither the journal nor the abstract is in oral medicine): This study focuses on 3D scanning and machine learning analysis of lingual papillae, belonging to basic research in taste/biology</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>边界情形，经研判属非口腔范畴（期刊与摘要均非口腔医学）：该研究聚焦于舌乳头（papillae）的3D扫描与机器学习分析，属于味觉/生物学基础研究</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60949,10 +60238,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The title explicitly labels it as a Systematic Review, belonging to the non-original research type, and does not meet the inclusion criteria of</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：标题明确标注为系统综述（Systematic Review），属于非原创研究类型，不符合纳入标准中的</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -60979,10 +60278,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article studies personalized dosimetry for yttrium-90 hepatic arterial radioembolization, belonging to the field of nuclear medicine therapy for liver tumors, and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献研究的是钇-90肝动脉放射栓塞的个性化剂量学，属于肝脏肿瘤核医学治疗领域，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61009,10 +60318,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article is a study on intracranial implants in the field of neuroscience, is unrelated to oral medicine, and does not involve the oral medicine scope.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献为神经科学领域的颅内植入物研究，与口腔医学无关，且未涉及口腔医学范畴。</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61039,10 +60358,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article is a study on biomimetic structural design in the field of bone tissue engineering/biomechanics. The abstract does not involve clinical practice or research in any discipline of oral medicine, and explicitly</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献为骨组织工程/生物力学领域的仿生结构设计研究，摘要未涉及口腔医学任何学科的临床实践或研究，明确</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61069,10 +60398,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article studies modeling of drug diffusion in three-dimensional space, belonging to the field of drug delivery/chemical engineering, and is unrelated to oral medicine, and does not involve any oral clinical</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献研究药物在三维空间中的扩散建模，属于药物递送/化学工程领域，与口腔医学无关，且未涉及任何口腔临</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61099,10 +60438,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article studies an electromechanical guidance system for breast biopsy, belonging to the field of breast imaging and intervention, and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献研究的是乳腺（breast）活检的机电引导系统，属于乳腺影像与介入领域，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61129,10 +60478,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article is an educational study on the development and implementation of a 3D printing elective course for health sciences students, belonging to educational literature, and does not involve any discipline of oral medicine</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献为面向健康科学学生的3D打印选修课程开发与实施的教学研究，属于教育类文献，未涉及口腔医学任何学</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61159,10 +60518,20 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Outside the oral medicine scope: This article is explicitly a study on neurosurgical preoperative planning, is unrelated to oral medicine, and in the abstract dentistry is only mentioned as an example of a 3D printing application field, and</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献明确为神经外科术前规划研究，与口腔医学无关，且摘要中仅将牙科作为3D打印应用领域的举例提及，并</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61189,10 +60558,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The study subject of this article is the developmental morphology of an amphibian (Thoropa miliaris tadpole), which has no relevance to oral medicine whatsoever,</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：该文献研究对象为两栖动物（Thoropa miliaris蝌蚪）的发育形态学，与口腔医学无任何关联，</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61219,10 +60598,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Document type = videoRecording (non-peer-reviewed original paper)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>文献类型=videoRecording（非同行评议原创论文）</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61249,10 +60638,20 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Outside the scope of oral medicine: The research topic of this study is the aesthetic evaluation of skin grafting at the radial forearm flap donor site, which belongs to the field of plastic surgery/head and neck reconstruction rather than oral medicine; and it does not involve</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该研究主题为前臂桡侧皮瓣供区的皮肤移植美学评估，属于整形外科/头颈重建领域，而非口腔医学范畴；且未涉</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61279,10 +60678,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The title and abstract of this article clearly indicate that it is a systematic review, which belongs to the non-original research category and does not meet</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：该文献标题和摘要明确表明为系统综述（systematic review），属于非原创研究类型，不符合</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61309,10 +60718,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Borderline case, upon assessment judged to be outside the oral medicine scope (neither the journal nor the abstract is in oral medicine): This article clearly belongs to the field of neurosurgical cranioplasty and is unrelated to oral medicine, not meeting the inclusion criterion of "oral medicine scope" in the</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>边界情形，经研判属非口腔范畴（期刊与摘要均非口腔医学）：该文献明确属于神经外科颅骨成形术领域，与口腔医学无关，不符合纳入标准中"口腔医学范畴"的</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61339,10 +60758,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Outside the scope of oral medicine: The topic of this article is auricular reconstruction for microtia (fabrication of auricular cartilage scaffolds), which belongs to the field of plastic surgery/ear reconstruction and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献主题为小耳症耳廓重建（耳廓软骨支架制作），属于整形外科/耳再造领域，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61369,10 +60798,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The title explicitly labels it as a "narrative review," which belongs to the review literature category and does not meet the criteria for original research papers</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：标题明确标注为"narrative review"（叙述性综述），属于综述类文献，不符合原创研究论文</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61399,10 +60838,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Outside the scope of oral medicine: This study is an orthopedic/neurosurgical study of spinal pedicle screw placement using 3D-printed spinal models and mixed reality navigation, and is unrelated to oral medicine.</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该研究为脊柱椎弓根螺钉置入的骨科/神经外科研究，使用3D打印脊柱模型和混合现实导航，与口腔医学无关。</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61429,10 +60878,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Review/meta-analysis (non-original research): The title and abstract of this article clearly indicate that it is a systematic review and meta-analysis (systematic review and me</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>综述/meta 分析（非原创研究）：该文献标题和摘要明确表明其为系统综述与meta分析（systematic review and me</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61459,10 +60918,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Borderline case, upon assessment judged to be outside the oral medicine scope (neither the journal nor the abstract is in oral medicine): This article is a study on tissue engineering and microfluidic microparticle delivery of growth factors, and the abstract does not involve the clinical practice or research of any discipline in oral medicine,</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>边界情形，经研判属非口腔范畴（期刊与摘要均非口腔医学）：该文献为组织工程与微流控微粒递送生长因子的研究，摘要未涉及口腔医学任何学科的临床实践或研</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61489,10 +60958,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Outside the scope of oral medicine: The topic of this article is neuroanatomy education and MRI training, which belongs to the field of neuroscience/medical education and is unrelated to oral medicine, clearly not meeting the PCC</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>非口腔医学范畴：该文献主题为神经解剖学教育与MRI训练，属于神经科学/医学教育领域，与口腔医学无关，明确不符合PCC</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61519,10 +60998,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Document type = preprint (non-peer-reviewed original paper)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>文献类型=preprint（非同行评议原创论文）</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>First round</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>第一轮</t>
         </is>
@@ -61549,10 +61038,20 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>Dental-specific CAD software only (does not meet Concept)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>仅用牙科专用 CAD 软件（不符 Concept）</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61579,10 +61078,20 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>3D-printed microfluidic chips only, no non-dental 3D software (does not meet Concept)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>仅用 3D 打印制微流控芯片、无非牙科 3D 软件（不符 Concept）</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61609,10 +61118,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>ICP image registration error methodology (non-oral)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>ICP 图像配准误差方法学（非口腔）</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61639,10 +61158,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>ProPlan CMF only (maxillofacial-specific software, does not meet Concept)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>仅用 ProPlan CMF（颌面专用软件，不符 Concept）</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61669,10 +61198,20 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>3D-printed glass sintering 4D analysis (materials science)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>3D 打印玻璃烧结 4D 分析（材料科学）</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61699,10 +61238,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Preclinical animal experiments for auricular reconstruction (ear reconstruction)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>耳廓重建临床前动物实验（耳再造）</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61729,10 +61278,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Mountain beaver skull morphometrics (zoology)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>山地海狸头骨形态测量（动物学）</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61759,10 +61318,20 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Mastoid air cell/sphenoid sinus measurements (otolaryngology)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>乳突气房/蝶窦测量（耳鼻喉科）</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61789,10 +61358,20 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Cranial defect implant design (neurosurgery)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>颅骨缺损植入物设计（神经外科）</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61819,10 +61398,20 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Microtia auricular reconstruction (plastic surgery)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>小耳症耳廓再造（整形外科）</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
@@ -61849,10 +61438,20 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Brain image de-identification (neuroimaging)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>脑部影像去识别化（神经影像）</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Second round</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>第二轮</t>
         </is>
